--- a/04_Figures/F06_prediction/modules/training/lasso/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/training/lasso/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -143,16 +143,10 @@
     <t xml:space="preserve">freq</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_black</t>
-  </si>
-  <si>
     <t xml:space="preserve">ME_blue</t>
   </si>
   <si>
     <t xml:space="preserve">ME_brown</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ME_green</t>
   </si>
   <si>
     <t xml:space="preserve">ME_greenyellow</t>
@@ -164,13 +158,16 @@
     <t xml:space="preserve">ME_pink</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_purple</t>
+    <t xml:space="preserve">ME_green</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon</t>
+    <t xml:space="preserve">ME_turquoise</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_tan</t>
+    <t xml:space="preserve">ME_black</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_purple</t>
   </si>
   <si>
     <t xml:space="preserve">ME_red</t>
@@ -563,7 +560,7 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -596,7 +593,7 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
@@ -608,16 +605,16 @@
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.213930348258706</v>
+        <v>0.169154228855721</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.320887117161399</v>
+        <v>-0.439985680998585</v>
       </c>
       <c r="M3" t="n">
-        <v>0.378006360121828</v>
+        <v>0.592498692623387</v>
       </c>
     </row>
     <row r="4">
@@ -637,7 +634,7 @@
         <v>14</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -670,7 +667,7 @@
         <v>14</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -682,16 +679,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.318407960199005</v>
+        <v>0.293532338308458</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.429534426574688</v>
+        <v>-0.491168862921602</v>
       </c>
       <c r="M5" t="n">
-        <v>0.573758893591804</v>
+        <v>0.572175580691326</v>
       </c>
     </row>
     <row r="6">
@@ -711,13 +708,13 @@
         <v>14</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.872696211177387</v>
+        <v>-0.383115871750001</v>
       </c>
       <c r="I6" t="n">
         <v>-0.986813186813187</v>
@@ -744,28 +741,28 @@
         <v>14</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.872696211177387</v>
+        <v>-0.383115871750001</v>
       </c>
       <c r="I7" t="n">
         <v>-0.986813186813187</v>
       </c>
       <c r="J7" t="n">
-        <v>0.890547263681592</v>
+        <v>0.512437810945274</v>
       </c>
       <c r="K7" t="n">
-        <v>0.517412935323383</v>
+        <v>0.572139303482587</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.40819408216778</v>
+        <v>-0.574728191904893</v>
       </c>
       <c r="M7" t="n">
-        <v>0.459832983094396</v>
+        <v>0.704799213455959</v>
       </c>
     </row>
     <row r="8">
@@ -785,13 +782,13 @@
         <v>14</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.230737427265299</v>
+        <v>-0.159763313609467</v>
       </c>
       <c r="I8" t="n">
         <v>-1</v>
@@ -818,28 +815,28 @@
         <v>14</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.230737427265299</v>
+        <v>-0.159763313609467</v>
       </c>
       <c r="I9" t="n">
         <v>-1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.606965174129353</v>
+        <v>0.318407960199005</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.367152512125194</v>
+        <v>-0.474603806914877</v>
       </c>
       <c r="M9" t="n">
-        <v>0.562663267184024</v>
+        <v>0.785694870390536</v>
       </c>
     </row>
     <row r="10">
@@ -859,16 +856,16 @@
         <v>14</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.03123723296939</v>
+        <v>-1.13122811291365</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.977934475965884</v>
+        <v>-0.974590990105923</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -892,28 +889,28 @@
         <v>14</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.03123723296939</v>
+        <v>-1.13122811291365</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.977934475965884</v>
+        <v>-0.974590990105923</v>
       </c>
       <c r="J11" t="n">
-        <v>0.930348258706468</v>
+        <v>0.875621890547264</v>
       </c>
       <c r="K11" t="n">
-        <v>0.54726368159204</v>
+        <v>0.527363184079602</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.38172352404825</v>
+        <v>-0.632020781754264</v>
       </c>
       <c r="M11" t="n">
-        <v>0.589285850971398</v>
+        <v>1.17103636480495</v>
       </c>
     </row>
     <row r="12">
@@ -933,16 +930,16 @@
         <v>13</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.28636939362934</v>
+        <v>-0.275163936604917</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.983425414364641</v>
+        <v>-0.751381215469613</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -966,28 +963,28 @@
         <v>13</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.28636939362934</v>
+        <v>-0.275163936604917</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.983425414364641</v>
+        <v>-0.751381215469613</v>
       </c>
       <c r="J13" t="n">
-        <v>0.567164179104478</v>
+        <v>0.512437810945274</v>
       </c>
       <c r="K13" t="n">
-        <v>0.507462686567164</v>
+        <v>0.298507462686567</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.3610162938925</v>
+        <v>-0.509954755872295</v>
       </c>
       <c r="M13" t="n">
-        <v>0.350017382521249</v>
+        <v>0.833590318224238</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1028,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.32697698621624</v>
       </c>
     </row>
     <row r="4">
@@ -1042,7 +1039,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.737465041938028</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="5">
@@ -1064,7 +1061,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.435381472605008</v>
+        <v>-0.80538843764289</v>
       </c>
     </row>
     <row r="7">
@@ -1075,7 +1072,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0652916568963442</v>
+        <v>0.611972069752436</v>
       </c>
     </row>
     <row r="8">
@@ -1086,7 +1083,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.204737583358807</v>
+        <v>-0.349494271259585</v>
       </c>
     </row>
     <row r="9">
@@ -1108,7 +1105,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.176566990593935</v>
+        <v>-0.390832230041315</v>
       </c>
     </row>
     <row r="11">
@@ -1119,7 +1116,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.238014134634715</v>
+        <v>-0.239283761221668</v>
       </c>
     </row>
     <row r="12">
@@ -1130,7 +1127,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.653525309824289</v>
+        <v>-0.0848283557033915</v>
       </c>
     </row>
     <row r="13">
@@ -1141,7 +1138,7 @@
         <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>0.589765370511414</v>
+        <v>-0.219325624472053</v>
       </c>
     </row>
     <row r="14">
@@ -1152,7 +1149,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-1.10217047477466</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="15">
@@ -1174,7 +1171,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.422405942461028</v>
+        <v>-0.720167747612611</v>
       </c>
     </row>
     <row r="17">
@@ -1207,7 +1204,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.159763313609468</v>
+        <v>-3.3767435145922</v>
       </c>
     </row>
     <row r="20">
@@ -1229,7 +1226,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.1770815098115</v>
+        <v>-0.179217271028226</v>
       </c>
     </row>
     <row r="22">
@@ -1251,7 +1248,7 @@
         <v>16</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.704586342292897</v>
+        <v>-0.423003566120981</v>
       </c>
     </row>
     <row r="24">
@@ -1262,7 +1259,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.18749322060055</v>
       </c>
     </row>
     <row r="25">
@@ -1273,7 +1270,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.980367882665292</v>
+        <v>-0.886533571602064</v>
       </c>
     </row>
     <row r="26">
@@ -1284,7 +1281,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.484447028820491</v>
+        <v>-0.433558161442998</v>
       </c>
     </row>
     <row r="27">
@@ -1295,7 +1292,7 @@
         <v>16</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.351154019681365</v>
+        <v>-0.169355890815354</v>
       </c>
     </row>
     <row r="28">
@@ -1306,7 +1303,7 @@
         <v>16</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.176013489239981</v>
+        <v>-0.49458230545754</v>
       </c>
     </row>
     <row r="29">
@@ -1317,7 +1314,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.255743269182324</v>
+        <v>-0.2460488185118</v>
       </c>
     </row>
     <row r="30">
@@ -1328,7 +1325,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.167206700016802</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="31">
@@ -1350,7 +1347,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.219936541221415</v>
+        <v>-0.418953662785959</v>
       </c>
     </row>
     <row r="33">
@@ -1361,7 +1358,7 @@
         <v>16</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.211824711362834</v>
+        <v>-0.247575328895103</v>
       </c>
     </row>
     <row r="34">
@@ -1372,7 +1369,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.474712695173943</v>
+        <v>-0.233825268511582</v>
       </c>
     </row>
     <row r="35">
@@ -1383,7 +1380,7 @@
         <v>16</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.36858396831257</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="36">
@@ -1394,7 +1391,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.05339350007307</v>
       </c>
     </row>
     <row r="37">
@@ -1405,7 +1402,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.363191760223464</v>
+        <v>-0.423751640948104</v>
       </c>
     </row>
     <row r="38">
@@ -1416,7 +1413,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.00858016536190442</v>
       </c>
     </row>
     <row r="39">
@@ -1427,7 +1424,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.532053300069361</v>
+        <v>-0.892237525303643</v>
       </c>
     </row>
     <row r="40">
@@ -1438,7 +1435,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.635719721046171</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="41">
@@ -1449,7 +1446,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.406932086659344</v>
+        <v>0.509756876250147</v>
       </c>
     </row>
     <row r="42">
@@ -1460,7 +1457,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.138554835296703</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="43">
@@ -1482,7 +1479,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.213870448451951</v>
+        <v>-0.170335864013595</v>
       </c>
     </row>
     <row r="45">
@@ -1493,7 +1490,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>-1.55363316271995</v>
+        <v>-0.221977665501389</v>
       </c>
     </row>
     <row r="46">
@@ -1504,7 +1501,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-0.333348270841124</v>
+        <v>-0.374689925024733</v>
       </c>
     </row>
     <row r="47">
@@ -1515,7 +1512,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.477382498629838</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="48">
@@ -1526,7 +1523,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.189699898259497</v>
+        <v>-3.48265433686412</v>
       </c>
     </row>
     <row r="49">
@@ -1537,7 +1534,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.383697043764625</v>
+        <v>-0.304923620974743</v>
       </c>
     </row>
     <row r="50">
@@ -1548,7 +1545,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.13286781750193</v>
       </c>
     </row>
     <row r="51">
@@ -1559,7 +1556,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.719553432721374</v>
+        <v>0.758632541268512</v>
       </c>
     </row>
     <row r="52">
@@ -1570,7 +1567,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.421522172743062</v>
+        <v>-0.515358941286822</v>
       </c>
     </row>
     <row r="53">
@@ -1581,7 +1578,7 @@
         <v>16</v>
       </c>
       <c r="C53" t="n">
-        <v>-0.567586075281551</v>
+        <v>-0.0525915895039983</v>
       </c>
     </row>
     <row r="54">
@@ -1592,7 +1589,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.08475289796358</v>
       </c>
     </row>
     <row r="55">
@@ -1603,7 +1600,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.454354851691629</v>
+        <v>-0.71210968561254</v>
       </c>
     </row>
     <row r="56">
@@ -1636,7 +1633,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.338822736196143</v>
+        <v>-0.556369917285735</v>
       </c>
     </row>
     <row r="59">
@@ -1647,7 +1644,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.394402518684705</v>
+        <v>-0.323447499991781</v>
       </c>
     </row>
     <row r="60">
@@ -1658,7 +1655,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.0164968070336462</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="61">
@@ -1669,7 +1666,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.405757104408286</v>
+        <v>-0.356967777259593</v>
       </c>
     </row>
     <row r="62">
@@ -1680,7 +1677,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.299121273673703</v>
+        <v>-3.64031109457104</v>
       </c>
     </row>
     <row r="63">
@@ -1691,7 +1688,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.218259604661751</v>
+        <v>-0.302733312631193</v>
       </c>
     </row>
     <row r="64">
@@ -1702,7 +1699,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.917903797560133</v>
+        <v>-0.485230030713155</v>
       </c>
     </row>
     <row r="65">
@@ -1713,7 +1710,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.906398645990522</v>
+        <v>-0.566405388288079</v>
       </c>
     </row>
     <row r="66">
@@ -1724,7 +1721,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.265385704548273</v>
+        <v>-0.0963480477784919</v>
       </c>
     </row>
     <row r="67">
@@ -1735,7 +1732,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.110651411789418</v>
+        <v>-0.12598656963055</v>
       </c>
     </row>
     <row r="68">
@@ -1746,7 +1743,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.214013146068295</v>
+        <v>-2.56571903225069</v>
       </c>
     </row>
     <row r="69">
@@ -1757,7 +1754,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.25438216831484</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="70">
@@ -1768,7 +1765,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.694401634761275</v>
       </c>
     </row>
     <row r="71">
@@ -1779,7 +1776,7 @@
         <v>16</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.482752135437144</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="72">
@@ -1790,7 +1787,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.363763185111318</v>
+        <v>-0.593815087405459</v>
       </c>
     </row>
     <row r="73">
@@ -1801,7 +1798,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>0.693026995713586</v>
+        <v>-0.620620681855889</v>
       </c>
     </row>
     <row r="74">
@@ -1812,7 +1809,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-1.14904071792536</v>
+        <v>-0.461244851265914</v>
       </c>
     </row>
     <row r="75">
@@ -1856,7 +1853,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.154076588684635</v>
       </c>
     </row>
     <row r="79">
@@ -1867,7 +1864,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.306419902583979</v>
+        <v>-0.211434483487208</v>
       </c>
     </row>
     <row r="80">
@@ -1889,7 +1886,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>-0.352426873070199</v>
+        <v>-0.312321675550568</v>
       </c>
     </row>
     <row r="82">
@@ -1900,7 +1897,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.395160236609223</v>
+        <v>-0.119613326230775</v>
       </c>
     </row>
     <row r="83">
@@ -1911,7 +1908,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.594388532222343</v>
+        <v>-0.323121617768374</v>
       </c>
     </row>
     <row r="84">
@@ -1922,7 +1919,7 @@
         <v>16</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.418300133085547</v>
+        <v>-0.515571422560454</v>
       </c>
     </row>
     <row r="85">
@@ -1933,7 +1930,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.273683423003281</v>
+        <v>-0.618063241770294</v>
       </c>
     </row>
     <row r="86">
@@ -1944,7 +1941,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>-0.169790777426467</v>
+        <v>-0.19392259124103</v>
       </c>
     </row>
     <row r="87">
@@ -1955,7 +1952,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.440676174901145</v>
       </c>
     </row>
     <row r="88">
@@ -1966,7 +1963,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-0.319346436780688</v>
+        <v>-0.142730531979571</v>
       </c>
     </row>
     <row r="89">
@@ -1977,7 +1974,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.217641722208906</v>
       </c>
     </row>
     <row r="90">
@@ -1988,7 +1985,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>0.078950242238154</v>
+        <v>-0.0979566782420935</v>
       </c>
     </row>
     <row r="91">
@@ -1999,7 +1996,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.696446373192254</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="92">
@@ -2010,7 +2007,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>0.331944830252642</v>
+        <v>-1.74001996571213</v>
       </c>
     </row>
     <row r="93">
@@ -2021,7 +2018,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>-0.635615422232785</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="94">
@@ -2032,7 +2029,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-1.15770592782044</v>
+        <v>-0.0594467938893373</v>
       </c>
     </row>
     <row r="95">
@@ -2043,7 +2040,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.594517275049002</v>
       </c>
     </row>
     <row r="96">
@@ -2054,7 +2051,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>-0.183949245601042</v>
+        <v>-1.0011664546811</v>
       </c>
     </row>
     <row r="97">
@@ -2065,7 +2062,7 @@
         <v>16</v>
       </c>
       <c r="C97" t="n">
-        <v>-0.0997089956435775</v>
+        <v>-0.05918157620479</v>
       </c>
     </row>
     <row r="98">
@@ -2076,7 +2073,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-0.575377764191318</v>
+        <v>-0.319850822602936</v>
       </c>
     </row>
     <row r="99">
@@ -2087,7 +2084,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-1.90825763939438</v>
+        <v>-0.282658519073895</v>
       </c>
     </row>
     <row r="100">
@@ -2098,7 +2095,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>-0.256001723393182</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="101">
@@ -2109,7 +2106,7 @@
         <v>16</v>
       </c>
       <c r="C101" t="n">
-        <v>-1.60930035171435</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="102">
@@ -2120,7 +2117,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.20767125577142</v>
       </c>
     </row>
     <row r="103">
@@ -2131,7 +2128,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.503936837660458</v>
       </c>
     </row>
     <row r="104">
@@ -2142,7 +2139,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.244505094029432</v>
       </c>
     </row>
     <row r="105">
@@ -2153,7 +2150,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.179047228228765</v>
+        <v>-1.43700803005611</v>
       </c>
     </row>
     <row r="106">
@@ -2164,7 +2161,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.59872489759329</v>
+        <v>-0.495758108306091</v>
       </c>
     </row>
     <row r="107">
@@ -2175,7 +2172,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.39176346994794</v>
+        <v>-1.13078489892743</v>
       </c>
     </row>
     <row r="108">
@@ -2186,7 +2183,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.2027457623277</v>
+        <v>-0.231445711618333</v>
       </c>
     </row>
     <row r="109">
@@ -2197,7 +2194,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.345650845813634</v>
       </c>
     </row>
     <row r="110">
@@ -2208,7 +2205,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.422307110717911</v>
+        <v>-0.648534152489124</v>
       </c>
     </row>
     <row r="111">
@@ -2219,7 +2216,7 @@
         <v>16</v>
       </c>
       <c r="C111" t="n">
-        <v>-0.362352197305228</v>
+        <v>-0.907781281971513</v>
       </c>
     </row>
     <row r="112">
@@ -2241,7 +2238,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.200135779869939</v>
+        <v>-1.02561652105047</v>
       </c>
     </row>
     <row r="114">
@@ -2252,7 +2249,7 @@
         <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>-0.239738041846168</v>
+        <v>-0.577391346331839</v>
       </c>
     </row>
     <row r="115">
@@ -2263,7 +2260,7 @@
         <v>16</v>
       </c>
       <c r="C115" t="n">
-        <v>-0.191868715519588</v>
+        <v>-0.191457753630456</v>
       </c>
     </row>
     <row r="116">
@@ -2285,7 +2282,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-0.15207082617992</v>
+        <v>-0.149424784093842</v>
       </c>
     </row>
     <row r="118">
@@ -2296,7 +2293,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.597562057636736</v>
       </c>
     </row>
     <row r="119">
@@ -2307,7 +2304,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.581103992027509</v>
+        <v>-0.666134663379987</v>
       </c>
     </row>
     <row r="120">
@@ -2318,7 +2315,7 @@
         <v>16</v>
       </c>
       <c r="C120" t="n">
-        <v>-0.811399479014643</v>
+        <v>-0.821597193904793</v>
       </c>
     </row>
     <row r="121">
@@ -2329,7 +2326,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.366027941749073</v>
       </c>
     </row>
     <row r="122">
@@ -2351,7 +2348,7 @@
         <v>16</v>
       </c>
       <c r="C123" t="n">
-        <v>-0.00669537057916458</v>
+        <v>-0.198325034194321</v>
       </c>
     </row>
     <row r="124">
@@ -2362,7 +2359,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-0.33725066371791</v>
+        <v>-0.405336479086823</v>
       </c>
     </row>
     <row r="125">
@@ -2373,7 +2370,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.725027623129872</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="126">
@@ -2384,7 +2381,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.218983690886293</v>
+        <v>-0.215795330482397</v>
       </c>
     </row>
     <row r="127">
@@ -2395,7 +2392,7 @@
         <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>-0.429633648222821</v>
+        <v>-0.213365378137483</v>
       </c>
     </row>
     <row r="128">
@@ -2406,7 +2403,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>-0.0659896957037396</v>
+        <v>-0.930152647577222</v>
       </c>
     </row>
     <row r="129">
@@ -2417,7 +2414,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.499517522562391</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="130">
@@ -2428,7 +2425,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-1.44964293540812</v>
+        <v>0.418051370455136</v>
       </c>
     </row>
     <row r="131">
@@ -2439,7 +2436,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.197538910098768</v>
+        <v>-0.253571821445194</v>
       </c>
     </row>
     <row r="132">
@@ -2450,7 +2447,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.54544918267154</v>
+        <v>-1.15337699941828</v>
       </c>
     </row>
     <row r="133">
@@ -2461,7 +2458,7 @@
         <v>16</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.693536148960949</v>
+        <v>-0.957743116520837</v>
       </c>
     </row>
     <row r="134">
@@ -2472,7 +2469,7 @@
         <v>16</v>
       </c>
       <c r="C134" t="n">
-        <v>-0.326583468325101</v>
+        <v>-0.255756485189538</v>
       </c>
     </row>
     <row r="135">
@@ -2483,7 +2480,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>-0.336693622715867</v>
+        <v>-1.58994651661707</v>
       </c>
     </row>
     <row r="136">
@@ -2494,7 +2491,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.5115784262794</v>
       </c>
     </row>
     <row r="137">
@@ -2505,7 +2502,7 @@
         <v>16</v>
       </c>
       <c r="C137" t="n">
-        <v>0.0288223569768482</v>
+        <v>-0.460597316094236</v>
       </c>
     </row>
     <row r="138">
@@ -2527,7 +2524,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>0.258344763747878</v>
+        <v>-0.631240040357372</v>
       </c>
     </row>
     <row r="140">
@@ -2538,7 +2535,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.143783052935456</v>
+        <v>-0.201223263787021</v>
       </c>
     </row>
     <row r="141">
@@ -2549,7 +2546,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.15894081308201</v>
+        <v>0.200057089686623</v>
       </c>
     </row>
     <row r="142">
@@ -2560,7 +2557,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.24759429885422</v>
+        <v>-1.03368350973384</v>
       </c>
     </row>
     <row r="143">
@@ -2571,7 +2568,7 @@
         <v>16</v>
       </c>
       <c r="C143" t="n">
-        <v>-0.172382008380642</v>
+        <v>-0.187765910364065</v>
       </c>
     </row>
     <row r="144">
@@ -2582,7 +2579,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.163578021941531</v>
       </c>
     </row>
     <row r="145">
@@ -2604,7 +2601,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.126889481134174</v>
+        <v>-0.215019983585804</v>
       </c>
     </row>
     <row r="147">
@@ -2626,7 +2623,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.291567794389685</v>
+        <v>-0.573646166036715</v>
       </c>
     </row>
     <row r="149">
@@ -2637,7 +2634,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.424072734591657</v>
+        <v>-0.557606079048346</v>
       </c>
     </row>
     <row r="150">
@@ -2648,7 +2645,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.186499516805501</v>
+        <v>-1.57558342733089</v>
       </c>
     </row>
     <row r="151">
@@ -2659,7 +2656,7 @@
         <v>16</v>
       </c>
       <c r="C151" t="n">
-        <v>-0.378248360344345</v>
+        <v>-0.506198562379925</v>
       </c>
     </row>
     <row r="152">
@@ -2670,7 +2667,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.742401702424876</v>
+        <v>-0.470733052399302</v>
       </c>
     </row>
     <row r="153">
@@ -2681,7 +2678,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.329833276813916</v>
+        <v>-0.269342277111496</v>
       </c>
     </row>
     <row r="154">
@@ -2703,7 +2700,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.442042236496963</v>
+        <v>-0.384710789503546</v>
       </c>
     </row>
     <row r="156">
@@ -2714,7 +2711,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.148192097212489</v>
+        <v>-0.704520241825796</v>
       </c>
     </row>
     <row r="157">
@@ -2725,7 +2722,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.616796539100031</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="158">
@@ -2736,7 +2733,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.441894578425407</v>
+        <v>-0.298463717991522</v>
       </c>
     </row>
     <row r="159">
@@ -2758,7 +2755,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.201164453346211</v>
+        <v>-0.995692832436408</v>
       </c>
     </row>
     <row r="161">
@@ -2769,7 +2766,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-1.06808214920256</v>
+        <v>-0.19716229367119</v>
       </c>
     </row>
     <row r="162">
@@ -2780,7 +2777,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.525917084059685</v>
+        <v>-0.738863255920694</v>
       </c>
     </row>
     <row r="163">
@@ -2813,7 +2810,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.208546919266661</v>
+        <v>0.000848932718592765</v>
       </c>
     </row>
     <row r="166">
@@ -2824,7 +2821,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>0.0297316257793805</v>
+        <v>0.372252907527877</v>
       </c>
     </row>
     <row r="167">
@@ -2846,7 +2843,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.627091110689874</v>
+        <v>-0.58567573508445</v>
       </c>
     </row>
     <row r="169">
@@ -2857,7 +2854,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>0.236840150252479</v>
+        <v>-1.22281630441544</v>
       </c>
     </row>
     <row r="170">
@@ -2868,7 +2865,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-2.05062687655843</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="171">
@@ -2879,7 +2876,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.41009640178928</v>
       </c>
     </row>
     <row r="172">
@@ -2890,7 +2887,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>0.336221924977917</v>
+        <v>-0.419907890328495</v>
       </c>
     </row>
     <row r="173">
@@ -2901,7 +2898,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.534306723949863</v>
+        <v>-0.374135272069901</v>
       </c>
     </row>
     <row r="174">
@@ -2912,7 +2909,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.311100074694241</v>
+        <v>-0.2486423403014</v>
       </c>
     </row>
     <row r="175">
@@ -2923,7 +2920,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.187890871588373</v>
+        <v>0.28271200917663</v>
       </c>
     </row>
     <row r="176">
@@ -2934,7 +2931,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-0.0630234417863291</v>
+        <v>-2.70767869662864</v>
       </c>
     </row>
     <row r="177">
@@ -2945,7 +2942,7 @@
         <v>16</v>
       </c>
       <c r="C177" t="n">
-        <v>-0.269629563793486</v>
+        <v>-0.21653926198623</v>
       </c>
     </row>
     <row r="178">
@@ -2956,7 +2953,7 @@
         <v>16</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.245727683880305</v>
+        <v>-0.664907019458962</v>
       </c>
     </row>
     <row r="179">
@@ -2967,7 +2964,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.333233026616576</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="180">
@@ -2978,7 +2975,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>0.165728010268863</v>
+        <v>-1.64875470808756</v>
       </c>
     </row>
     <row r="181">
@@ -2989,7 +2986,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.741103453307324</v>
+        <v>-0.446783885773423</v>
       </c>
     </row>
     <row r="182">
@@ -3000,7 +2997,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>-1.21814957491021</v>
+        <v>-0.515378793991699</v>
       </c>
     </row>
     <row r="183">
@@ -3011,7 +3008,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-0.296724112927067</v>
+        <v>-0.266707702390652</v>
       </c>
     </row>
     <row r="184">
@@ -3022,7 +3019,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.402639596201768</v>
+        <v>-0.857627110767346</v>
       </c>
     </row>
     <row r="185">
@@ -3033,7 +3030,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>0.269944495903622</v>
+        <v>0.494348366966408</v>
       </c>
     </row>
     <row r="186">
@@ -3044,7 +3041,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>0.704139047999879</v>
+        <v>0.651728921912208</v>
       </c>
     </row>
     <row r="187">
@@ -3055,7 +3052,7 @@
         <v>16</v>
       </c>
       <c r="C187" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.459016786149036</v>
       </c>
     </row>
     <row r="188">
@@ -3066,7 +3063,7 @@
         <v>16</v>
       </c>
       <c r="C188" t="n">
-        <v>0.35536804935193</v>
+        <v>-0.297862625058329</v>
       </c>
     </row>
     <row r="189">
@@ -3077,7 +3074,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>0.105321878022812</v>
+        <v>0.335135983453011</v>
       </c>
     </row>
     <row r="190">
@@ -3088,7 +3085,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>0.592142349479801</v>
+        <v>0.103636312871553</v>
       </c>
     </row>
     <row r="191">
@@ -3110,7 +3107,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-1.28379746302626</v>
+        <v>-0.362443190006223</v>
       </c>
     </row>
     <row r="193">
@@ -3121,7 +3118,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.241740688286136</v>
       </c>
     </row>
     <row r="194">
@@ -3132,7 +3129,7 @@
         <v>16</v>
       </c>
       <c r="C194" t="n">
-        <v>-0.509019852948948</v>
+        <v>-0.388622497002787</v>
       </c>
     </row>
     <row r="195">
@@ -3143,7 +3140,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.422020954247119</v>
+        <v>-0.177145016773824</v>
       </c>
     </row>
     <row r="196">
@@ -3154,7 +3151,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.3643799628707</v>
       </c>
     </row>
     <row r="197">
@@ -3165,7 +3162,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.590171032808859</v>
       </c>
     </row>
     <row r="198">
@@ -3176,7 +3173,7 @@
         <v>16</v>
       </c>
       <c r="C198" t="n">
-        <v>-1.14317730271379</v>
+        <v>-1.03567392328405</v>
       </c>
     </row>
     <row r="199">
@@ -3187,7 +3184,7 @@
         <v>16</v>
       </c>
       <c r="C199" t="n">
-        <v>-0.212502530297926</v>
+        <v>-0.129044303420013</v>
       </c>
     </row>
     <row r="200">
@@ -3198,7 +3195,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-0.297319569436456</v>
+        <v>-0.397186697607721</v>
       </c>
     </row>
     <row r="201">
@@ -3220,7 +3217,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.965697227989391</v>
+        <v>-2.25859166666495</v>
       </c>
     </row>
     <row r="203">
@@ -3231,7 +3228,7 @@
         <v>16</v>
       </c>
       <c r="C203" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.566207131706308</v>
       </c>
     </row>
     <row r="204">
@@ -3242,7 +3239,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-0.200034399264148</v>
+        <v>-0.95342807619486</v>
       </c>
     </row>
     <row r="205">
@@ -3264,7 +3261,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.198811171791611</v>
+        <v>-0.360469437397032</v>
       </c>
     </row>
     <row r="207">
@@ -3275,7 +3272,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.27541605200044</v>
+        <v>-0.0780632263664465</v>
       </c>
     </row>
     <row r="208">
@@ -3286,7 +3283,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.667099520698382</v>
+        <v>-0.520266283921641</v>
       </c>
     </row>
     <row r="209">
@@ -3308,7 +3305,7 @@
         <v>16</v>
       </c>
       <c r="C210" t="n">
-        <v>-0.363549442792288</v>
+        <v>-0.224859095499782</v>
       </c>
     </row>
     <row r="211">
@@ -3319,7 +3316,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.192245162461915</v>
+        <v>-0.173088068589926</v>
       </c>
     </row>
     <row r="212">
@@ -3330,7 +3327,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.767434645415151</v>
+        <v>0.101583436898331</v>
       </c>
     </row>
     <row r="213">
@@ -3341,7 +3338,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.108332391000749</v>
+        <v>0.153546743589272</v>
       </c>
     </row>
     <row r="214">
@@ -3374,7 +3371,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-0.218597032160375</v>
+        <v>-0.409766772983035</v>
       </c>
     </row>
     <row r="217">
@@ -3385,7 +3382,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.452183777651376</v>
+        <v>-0.221898025022931</v>
       </c>
     </row>
     <row r="218">
@@ -3396,7 +3393,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.557687987824888</v>
+        <v>-0.281034405043691</v>
       </c>
     </row>
     <row r="219">
@@ -3407,7 +3404,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.682327625114402</v>
       </c>
     </row>
     <row r="220">
@@ -3418,7 +3415,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.506489598134535</v>
       </c>
     </row>
     <row r="221">
@@ -3429,7 +3426,7 @@
         <v>16</v>
       </c>
       <c r="C221" t="n">
-        <v>-0.252519027407411</v>
+        <v>-0.180906353921379</v>
       </c>
     </row>
     <row r="222">
@@ -3440,7 +3437,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-1.84593096583099</v>
+        <v>-0.984182592023015</v>
       </c>
     </row>
     <row r="223">
@@ -3451,7 +3448,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.816015773495675</v>
+        <v>-0.801744900211026</v>
       </c>
     </row>
     <row r="224">
@@ -3473,7 +3470,7 @@
         <v>16</v>
       </c>
       <c r="C225" t="n">
-        <v>-0.16693178684254</v>
+        <v>-0.94639701532328</v>
       </c>
     </row>
     <row r="226">
@@ -3484,7 +3481,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>-0.354821226696458</v>
+        <v>-0.732082007650116</v>
       </c>
     </row>
     <row r="227">
@@ -3506,7 +3503,7 @@
         <v>16</v>
       </c>
       <c r="C228" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.725435666352599</v>
       </c>
     </row>
     <row r="229">
@@ -3517,7 +3514,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.237632161569402</v>
+        <v>-0.181680565255111</v>
       </c>
     </row>
     <row r="230">
@@ -3528,7 +3525,7 @@
         <v>16</v>
       </c>
       <c r="C230" t="n">
-        <v>-0.462643376909006</v>
+        <v>-0.268453301020032</v>
       </c>
     </row>
     <row r="231">
@@ -3550,7 +3547,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.210497684744037</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="233">
@@ -3561,7 +3558,7 @@
         <v>16</v>
       </c>
       <c r="C233" t="n">
-        <v>-0.570177152472511</v>
+        <v>-0.185761319082683</v>
       </c>
     </row>
     <row r="234">
@@ -3572,7 +3569,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.210705068027385</v>
+        <v>-0.356042393814379</v>
       </c>
     </row>
     <row r="235">
@@ -3583,7 +3580,7 @@
         <v>16</v>
       </c>
       <c r="C235" t="n">
-        <v>-0.169140244971698</v>
+        <v>-0.692212046646478</v>
       </c>
     </row>
     <row r="236">
@@ -3594,7 +3591,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.08671195933697</v>
       </c>
     </row>
     <row r="237">
@@ -3605,7 +3602,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.650382568212079</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="238">
@@ -3616,7 +3613,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.255371220576839</v>
+        <v>-0.604925046374381</v>
       </c>
     </row>
     <row r="239">
@@ -3638,7 +3635,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.502897663096549</v>
       </c>
     </row>
     <row r="241">
@@ -3649,7 +3646,7 @@
         <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>-1.2198707674661</v>
+        <v>-0.318093332477145</v>
       </c>
     </row>
     <row r="242">
@@ -3671,7 +3668,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.38242601364458</v>
+        <v>-1.07427485256425</v>
       </c>
     </row>
     <row r="244">
@@ -3682,7 +3679,7 @@
         <v>16</v>
       </c>
       <c r="C244" t="n">
-        <v>-1.57273806292549</v>
+        <v>-0.544258979238541</v>
       </c>
     </row>
     <row r="245">
@@ -3693,7 +3690,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.397289679282152</v>
+        <v>-0.596875223804216</v>
       </c>
     </row>
     <row r="246">
@@ -3704,7 +3701,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-0.751331921721922</v>
+        <v>-0.63558650455121</v>
       </c>
     </row>
     <row r="247">
@@ -3715,7 +3712,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.499146981402937</v>
       </c>
     </row>
     <row r="248">
@@ -3726,7 +3723,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.27563298806775</v>
       </c>
     </row>
     <row r="249">
@@ -3737,7 +3734,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.48879547254061</v>
+        <v>-1.16130492011123</v>
       </c>
     </row>
     <row r="250">
@@ -3748,7 +3745,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.174771729426392</v>
       </c>
     </row>
     <row r="251">
@@ -3759,7 +3756,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.454692712248895</v>
+        <v>-1.14312915535352</v>
       </c>
     </row>
     <row r="252">
@@ -3770,7 +3767,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.38571596122497</v>
+        <v>-0.694939916051575</v>
       </c>
     </row>
     <row r="253">
@@ -3781,7 +3778,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.875352270146365</v>
       </c>
     </row>
     <row r="254">
@@ -3792,7 +3789,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.306781058256618</v>
+        <v>-0.811350760211554</v>
       </c>
     </row>
     <row r="255">
@@ -3803,7 +3800,7 @@
         <v>16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.269426108749892</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="256">
@@ -3814,7 +3811,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.183497793667728</v>
+        <v>-0.18823076761282</v>
       </c>
     </row>
     <row r="257">
@@ -3836,7 +3833,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.424063208575448</v>
       </c>
     </row>
     <row r="259">
@@ -3847,7 +3844,7 @@
         <v>16</v>
       </c>
       <c r="C259" t="n">
-        <v>-0.198138921337876</v>
+        <v>-0.216322632535023</v>
       </c>
     </row>
     <row r="260">
@@ -3858,7 +3855,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.476462409558863</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="261">
@@ -3869,7 +3866,7 @@
         <v>16</v>
       </c>
       <c r="C261" t="n">
-        <v>-0.395310748908455</v>
+        <v>-0.290941347471988</v>
       </c>
     </row>
     <row r="262">
@@ -3880,7 +3877,7 @@
         <v>16</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.261775269949744</v>
+        <v>-1.22587186784022</v>
       </c>
     </row>
     <row r="263">
@@ -3902,7 +3899,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.18898108629836</v>
+        <v>-0.901887903794021</v>
       </c>
     </row>
     <row r="265">
@@ -3913,7 +3910,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.358994871380588</v>
+        <v>-0.558072027050188</v>
       </c>
     </row>
     <row r="266">
@@ -3924,7 +3921,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-0.211934646905393</v>
+        <v>-0.357884467914027</v>
       </c>
     </row>
     <row r="267">
@@ -3935,7 +3932,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-1.43266698572582</v>
+        <v>-2.99132628943376</v>
       </c>
     </row>
     <row r="268">
@@ -3946,7 +3943,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>-0.0529598486909775</v>
+        <v>-0.690060810031555</v>
       </c>
     </row>
     <row r="269">
@@ -3957,7 +3954,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.191033138838492</v>
+        <v>-0.194380609833018</v>
       </c>
     </row>
     <row r="270">
@@ -3968,7 +3965,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.605621229607597</v>
       </c>
     </row>
     <row r="271">
@@ -3979,7 +3976,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.304831829701357</v>
+        <v>-1.28522578630639</v>
       </c>
     </row>
     <row r="272">
@@ -3990,7 +3987,7 @@
         <v>16</v>
       </c>
       <c r="C272" t="n">
-        <v>-1.40918819862322</v>
+        <v>-0.958567793043817</v>
       </c>
     </row>
     <row r="273">
@@ -4001,7 +3998,7 @@
         <v>16</v>
       </c>
       <c r="C273" t="n">
-        <v>-0.22459380091803</v>
+        <v>-0.681825536587334</v>
       </c>
     </row>
     <row r="274">
@@ -4012,7 +4009,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.688790832734356</v>
+        <v>-0.75269882602376</v>
       </c>
     </row>
     <row r="275">
@@ -4023,7 +4020,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.226710373366962</v>
+        <v>-0.221263475267636</v>
       </c>
     </row>
     <row r="276">
@@ -4034,7 +4031,7 @@
         <v>16</v>
       </c>
       <c r="C276" t="n">
-        <v>-0.411914656484205</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="277">
@@ -4056,7 +4053,7 @@
         <v>16</v>
       </c>
       <c r="C278" t="n">
-        <v>-0.185142497246844</v>
+        <v>-0.443092304474478</v>
       </c>
     </row>
     <row r="279">
@@ -4067,7 +4064,7 @@
         <v>16</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.257578698687944</v>
+        <v>-1.70481238529429</v>
       </c>
     </row>
     <row r="280">
@@ -4089,7 +4086,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>-0.279443410743132</v>
+        <v>-2.3517936224172</v>
       </c>
     </row>
     <row r="282">
@@ -4100,7 +4097,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.159763313609467</v>
+        <v>0.142558533523719</v>
       </c>
     </row>
     <row r="283">
@@ -4111,7 +4108,7 @@
         <v>16</v>
       </c>
       <c r="C283" t="n">
-        <v>-0.687503144787885</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="284">
@@ -4122,7 +4119,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.314011909818046</v>
+        <v>-0.724053092584965</v>
       </c>
     </row>
     <row r="285">
@@ -4133,7 +4130,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.351180567310725</v>
       </c>
     </row>
     <row r="286">
@@ -4144,7 +4141,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>-0.175274389162614</v>
+        <v>-0.293790795561414</v>
       </c>
     </row>
     <row r="287">
@@ -4155,7 +4152,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.0938835305175831</v>
       </c>
     </row>
     <row r="288">
@@ -4166,7 +4163,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-1.00286426312997</v>
+        <v>-0.336021329953843</v>
       </c>
     </row>
     <row r="289">
@@ -4177,7 +4174,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>-0.66210422533293</v>
+        <v>-0.22120959376001</v>
       </c>
     </row>
     <row r="290">
@@ -4188,7 +4185,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.310387184567201</v>
+        <v>-0.493268879748822</v>
       </c>
     </row>
     <row r="291">
@@ -4199,7 +4196,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-0.24300648571459</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="292">
@@ -4210,7 +4207,7 @@
         <v>16</v>
       </c>
       <c r="C292" t="n">
-        <v>-0.683414791681617</v>
+        <v>-1.27996478859528</v>
       </c>
     </row>
     <row r="293">
@@ -4221,7 +4218,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.341786254722087</v>
       </c>
     </row>
     <row r="294">
@@ -4232,7 +4229,7 @@
         <v>16</v>
       </c>
       <c r="C294" t="n">
-        <v>-0.162009267004845</v>
+        <v>-0.508047806516946</v>
       </c>
     </row>
     <row r="295">
@@ -4243,7 +4240,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.168113854032284</v>
+        <v>-0.233123781791161</v>
       </c>
     </row>
     <row r="296">
@@ -4254,7 +4251,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>-0.868967606987423</v>
+        <v>-0.538018170755081</v>
       </c>
     </row>
     <row r="297">
@@ -4265,7 +4262,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="n">
-        <v>0.662592636737067</v>
+        <v>0.470419884882501</v>
       </c>
     </row>
     <row r="298">
@@ -4276,7 +4273,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-2.4509900997348</v>
+        <v>-0.444968734429339</v>
       </c>
     </row>
     <row r="299">
@@ -4287,7 +4284,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.47662683963097</v>
       </c>
     </row>
     <row r="300">
@@ -4298,7 +4295,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>-0.294263100417953</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="301">
@@ -4309,7 +4306,7 @@
         <v>16</v>
       </c>
       <c r="C301" t="n">
-        <v>-0.334684726155414</v>
+        <v>-0.77560194996818</v>
       </c>
     </row>
     <row r="302">
@@ -4320,7 +4317,7 @@
         <v>16</v>
       </c>
       <c r="C302" t="n">
-        <v>-0.394817792980771</v>
+        <v>-0.747954858223687</v>
       </c>
     </row>
     <row r="303">
@@ -4342,7 +4339,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.313016922213352</v>
       </c>
     </row>
     <row r="305">
@@ -4364,7 +4361,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.195635441561621</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="307">
@@ -4375,7 +4372,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.124169712368566</v>
+        <v>0.064411550741911</v>
       </c>
     </row>
     <row r="308">
@@ -4386,7 +4383,7 @@
         <v>16</v>
       </c>
       <c r="C308" t="n">
-        <v>-0.264738478313131</v>
+        <v>-0.327941095338959</v>
       </c>
     </row>
     <row r="309">
@@ -4397,7 +4394,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.743189855168375</v>
       </c>
     </row>
     <row r="310">
@@ -4408,7 +4405,7 @@
         <v>16</v>
       </c>
       <c r="C310" t="n">
-        <v>-0.309691971414897</v>
+        <v>-0.698281631947837</v>
       </c>
     </row>
     <row r="311">
@@ -4419,7 +4416,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.233515040527432</v>
       </c>
     </row>
     <row r="312">
@@ -4430,7 +4427,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.911884570349149</v>
+        <v>-0.748703018858627</v>
       </c>
     </row>
     <row r="313">
@@ -4441,7 +4438,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.191356814812621</v>
+        <v>-0.587409203074274</v>
       </c>
     </row>
     <row r="314">
@@ -4452,7 +4449,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-0.162757693134898</v>
+        <v>-0.276264478176793</v>
       </c>
     </row>
     <row r="315">
@@ -4463,7 +4460,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-0.183939153769155</v>
+        <v>-0.0893352111565544</v>
       </c>
     </row>
     <row r="316">
@@ -4485,7 +4482,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.312867956505567</v>
+        <v>-0.270439059844136</v>
       </c>
     </row>
     <row r="318">
@@ -4496,7 +4493,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.97657608880545</v>
       </c>
     </row>
     <row r="319">
@@ -4507,7 +4504,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.499260356083193</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="320">
@@ -4518,7 +4515,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.478584985781295</v>
+        <v>-0.663357638536091</v>
       </c>
     </row>
     <row r="321">
@@ -4529,7 +4526,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-2.40514463052537</v>
+        <v>-0.334180033857723</v>
       </c>
     </row>
     <row r="322">
@@ -4540,7 +4537,7 @@
         <v>16</v>
       </c>
       <c r="C322" t="n">
-        <v>-0.485628953490376</v>
+        <v>-0.341863892742431</v>
       </c>
     </row>
     <row r="323">
@@ -4551,7 +4548,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>0.116627719868912</v>
+        <v>-0.39314396696419</v>
       </c>
     </row>
     <row r="324">
@@ -4562,7 +4559,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.389973022099487</v>
+        <v>-0.462357947864358</v>
       </c>
     </row>
     <row r="325">
@@ -4573,7 +4570,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.252929781187662</v>
+        <v>-0.276943697983206</v>
       </c>
     </row>
     <row r="326">
@@ -4584,7 +4581,7 @@
         <v>16</v>
       </c>
       <c r="C326" t="n">
-        <v>-1.46304074572546</v>
+        <v>-0.171123990724197</v>
       </c>
     </row>
     <row r="327">
@@ -4606,7 +4603,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>-0.55684554426308</v>
+        <v>-0.494501334796426</v>
       </c>
     </row>
     <row r="329">
@@ -4617,7 +4614,7 @@
         <v>16</v>
       </c>
       <c r="C329" t="n">
-        <v>-0.418101229269599</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="330">
@@ -4628,7 +4625,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.718884837940951</v>
+        <v>0.132216032285708</v>
       </c>
     </row>
     <row r="331">
@@ -4639,7 +4636,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.170568240710836</v>
       </c>
     </row>
     <row r="332">
@@ -4650,7 +4647,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.405851662959326</v>
+        <v>-0.248586170464115</v>
       </c>
     </row>
     <row r="333">
@@ -4661,7 +4658,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.65360385573922</v>
+        <v>-0.908990367249449</v>
       </c>
     </row>
     <row r="334">
@@ -4672,7 +4669,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.346092993258654</v>
+        <v>-0.1700299949821</v>
       </c>
     </row>
     <row r="335">
@@ -4683,7 +4680,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.234413061991056</v>
       </c>
     </row>
     <row r="336">
@@ -4694,7 +4691,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.544369286876363</v>
+        <v>-1.38916557104282</v>
       </c>
     </row>
     <row r="337">
@@ -4705,7 +4702,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.126199703083365</v>
+        <v>-0.156870218362398</v>
       </c>
     </row>
     <row r="338">
@@ -4716,7 +4713,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>-0.216812874082699</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="339">
@@ -4727,7 +4724,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>-0.208463325864645</v>
+        <v>-0.233843898944596</v>
       </c>
     </row>
     <row r="340">
@@ -4738,7 +4735,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.218352817100801</v>
+        <v>-0.55437376182249</v>
       </c>
     </row>
     <row r="341">
@@ -4749,7 +4746,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.175316651642463</v>
+        <v>-0.188798542539665</v>
       </c>
     </row>
     <row r="342">
@@ -4760,7 +4757,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.232266859866725</v>
+        <v>-1.83089003644781</v>
       </c>
     </row>
     <row r="343">
@@ -4771,7 +4768,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-1.49280370711486</v>
+        <v>-0.225381428779875</v>
       </c>
     </row>
     <row r="344">
@@ -4804,7 +4801,7 @@
         <v>16</v>
       </c>
       <c r="C346" t="n">
-        <v>0.0696625433649826</v>
+        <v>0.106627450160355</v>
       </c>
     </row>
     <row r="347">
@@ -4815,7 +4812,7 @@
         <v>16</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.348901919033643</v>
+        <v>-1.23581943014801</v>
       </c>
     </row>
     <row r="348">
@@ -4826,7 +4823,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>0.0720007763355944</v>
+        <v>0.10484158292783</v>
       </c>
     </row>
     <row r="349">
@@ -4837,7 +4834,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.319363090666137</v>
+        <v>-0.432435176412929</v>
       </c>
     </row>
     <row r="350">
@@ -4848,7 +4845,7 @@
         <v>16</v>
       </c>
       <c r="C350" t="n">
-        <v>-0.647812635980046</v>
+        <v>-0.894705346910925</v>
       </c>
     </row>
     <row r="351">
@@ -4859,7 +4856,7 @@
         <v>16</v>
       </c>
       <c r="C351" t="n">
-        <v>-1.09720557736433</v>
+        <v>-0.340802874403171</v>
       </c>
     </row>
     <row r="352">
@@ -4870,7 +4867,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.572210396171956</v>
+        <v>-0.500107560124142</v>
       </c>
     </row>
     <row r="353">
@@ -4881,7 +4878,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>0.11507186555562</v>
+        <v>0.584634331762573</v>
       </c>
     </row>
     <row r="354">
@@ -4903,7 +4900,7 @@
         <v>16</v>
       </c>
       <c r="C355" t="n">
-        <v>-0.49962029118062</v>
+        <v>-0.342565535194801</v>
       </c>
     </row>
     <row r="356">
@@ -4914,7 +4911,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>-1.47747031793649</v>
+        <v>-1.07131475408117</v>
       </c>
     </row>
     <row r="357">
@@ -4925,7 +4922,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-1.49738217527952</v>
+        <v>-0.763486223662535</v>
       </c>
     </row>
     <row r="358">
@@ -4936,7 +4933,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-0.389867687540979</v>
+        <v>-0.184025375395928</v>
       </c>
     </row>
     <row r="359">
@@ -4947,7 +4944,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.159763313609467</v>
+        <v>-3.28282098528922</v>
       </c>
     </row>
     <row r="360">
@@ -4958,7 +4955,7 @@
         <v>16</v>
       </c>
       <c r="C360" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.614203028774156</v>
       </c>
     </row>
     <row r="361">
@@ -4969,7 +4966,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.177004828781981</v>
       </c>
     </row>
     <row r="362">
@@ -4980,7 +4977,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.274350429727122</v>
+        <v>-0.341408334255838</v>
       </c>
     </row>
     <row r="363">
@@ -5002,7 +4999,7 @@
         <v>16</v>
       </c>
       <c r="C364" t="n">
-        <v>-0.253916611499782</v>
+        <v>-0.20241650743111</v>
       </c>
     </row>
     <row r="365">
@@ -5013,7 +5010,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.278270762027538</v>
+        <v>-0.14255921517622</v>
       </c>
     </row>
     <row r="366">
@@ -5024,7 +5021,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.180893600505116</v>
+        <v>-1.22511898652424</v>
       </c>
     </row>
     <row r="367">
@@ -5035,7 +5032,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-4.11162954045937</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="368">
@@ -5046,7 +5043,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.614834436803667</v>
+        <v>-2.20187876924589</v>
       </c>
     </row>
     <row r="369">
@@ -5057,7 +5054,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.255962170918712</v>
+        <v>-1.26851125127291</v>
       </c>
     </row>
     <row r="370">
@@ -5068,7 +5065,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.518874408568548</v>
+        <v>-0.878855553547941</v>
       </c>
     </row>
     <row r="371">
@@ -5079,7 +5076,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.184849795602599</v>
+        <v>-0.204196157261833</v>
       </c>
     </row>
     <row r="372">
@@ -5090,7 +5087,7 @@
         <v>16</v>
       </c>
       <c r="C372" t="n">
-        <v>-0.28664831186971</v>
+        <v>-0.268804417889872</v>
       </c>
     </row>
     <row r="373">
@@ -5101,7 +5098,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.183709217395516</v>
+        <v>-0.707291429122799</v>
       </c>
     </row>
     <row r="374">
@@ -5112,7 +5109,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.248892328076689</v>
+        <v>-0.264716618880934</v>
       </c>
     </row>
     <row r="375">
@@ -5123,7 +5120,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>0.343494937250047</v>
+        <v>0.47659676025875</v>
       </c>
     </row>
     <row r="376">
@@ -5134,7 +5131,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.703563806165309</v>
+        <v>-0.22370716853908</v>
       </c>
     </row>
     <row r="377">
@@ -5145,7 +5142,7 @@
         <v>16</v>
       </c>
       <c r="C377" t="n">
-        <v>-0.262160483032314</v>
+        <v>-0.248703759207713</v>
       </c>
     </row>
     <row r="378">
@@ -5156,7 +5153,7 @@
         <v>16</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.482833648169687</v>
+        <v>-0.211574226890662</v>
       </c>
     </row>
     <row r="379">
@@ -5167,7 +5164,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.594457128752843</v>
+        <v>-0.315520367153042</v>
       </c>
     </row>
     <row r="380">
@@ -5178,7 +5175,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>-0.504553975548632</v>
+        <v>-0.433950480953945</v>
       </c>
     </row>
     <row r="381">
@@ -5189,7 +5186,7 @@
         <v>16</v>
       </c>
       <c r="C381" t="n">
-        <v>-0.313025045903926</v>
+        <v>-0.369955296426492</v>
       </c>
     </row>
     <row r="382">
@@ -5200,7 +5197,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.831007644574562</v>
+        <v>-0.656803383380161</v>
       </c>
     </row>
     <row r="383">
@@ -5211,7 +5208,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.197666963853881</v>
+        <v>-0.196678425648123</v>
       </c>
     </row>
     <row r="384">
@@ -5222,7 +5219,7 @@
         <v>16</v>
       </c>
       <c r="C384" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.232909562823767</v>
       </c>
     </row>
     <row r="385">
@@ -5233,7 +5230,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.381360423447787</v>
+        <v>0.00823895751652048</v>
       </c>
     </row>
     <row r="386">
@@ -5244,7 +5241,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.0368938765566811</v>
+        <v>-0.0637049838440094</v>
       </c>
     </row>
     <row r="387">
@@ -5255,7 +5252,7 @@
         <v>16</v>
       </c>
       <c r="C387" t="n">
-        <v>-0.194111818181514</v>
+        <v>-0.870108594209405</v>
       </c>
     </row>
     <row r="388">
@@ -5266,7 +5263,7 @@
         <v>16</v>
       </c>
       <c r="C388" t="n">
-        <v>0.322468455520102</v>
+        <v>-0.344156362198059</v>
       </c>
     </row>
     <row r="389">
@@ -5277,7 +5274,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.107622011700719</v>
+        <v>-0.0814070359820616</v>
       </c>
     </row>
     <row r="390">
@@ -5288,7 +5285,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-0.139305484159987</v>
+        <v>-0.218659467995783</v>
       </c>
     </row>
     <row r="391">
@@ -5299,7 +5296,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.226533290782846</v>
+        <v>-0.626489867390744</v>
       </c>
     </row>
     <row r="392">
@@ -5310,7 +5307,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.559169747817505</v>
+        <v>-0.122709927622418</v>
       </c>
     </row>
     <row r="393">
@@ -5332,7 +5329,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-0.562071572966802</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="395">
@@ -5343,7 +5340,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>-0.868863454412831</v>
+        <v>-0.255546748410785</v>
       </c>
     </row>
     <row r="396">
@@ -5354,7 +5351,7 @@
         <v>16</v>
       </c>
       <c r="C396" t="n">
-        <v>-0.689934145630806</v>
+        <v>-1.22986769780932</v>
       </c>
     </row>
     <row r="397">
@@ -5365,7 +5362,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>-4.28963307272409</v>
+        <v>-1.2678683850587</v>
       </c>
     </row>
     <row r="398">
@@ -5376,7 +5373,7 @@
         <v>16</v>
       </c>
       <c r="C398" t="n">
-        <v>-2.03664059588955</v>
+        <v>-3.92516939350935</v>
       </c>
     </row>
     <row r="399">
@@ -5398,7 +5395,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.323708370585844</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="401">
@@ -5409,7 +5406,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>-2.03599899930057</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="402">
@@ -5420,7 +5417,7 @@
         <v>16</v>
       </c>
       <c r="C402" t="n">
-        <v>-0.578354238254049</v>
+        <v>-2.66064289679969</v>
       </c>
     </row>
     <row r="403">
@@ -5442,7 +5439,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.378493981223596</v>
       </c>
     </row>
     <row r="405">
@@ -5464,7 +5461,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.460781282290988</v>
       </c>
     </row>
     <row r="407">
@@ -5475,7 +5472,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.85877400919099</v>
+        <v>-2.45710084575134</v>
       </c>
     </row>
     <row r="408">
@@ -5486,7 +5483,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.431028196130365</v>
+        <v>-0.431136144738571</v>
       </c>
     </row>
     <row r="409">
@@ -5508,7 +5505,7 @@
         <v>16</v>
       </c>
       <c r="C410" t="n">
-        <v>-0.272775202832994</v>
+        <v>-0.266278963295992</v>
       </c>
     </row>
     <row r="411">
@@ -5530,7 +5527,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.615340956642305</v>
+        <v>0.0496759926493153</v>
       </c>
     </row>
     <row r="413">
@@ -5541,7 +5538,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.234589307037143</v>
+        <v>0.0799420839691851</v>
       </c>
     </row>
     <row r="414">
@@ -5552,7 +5549,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-0.470684126073505</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="415">
@@ -5563,7 +5560,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.446727015705999</v>
+        <v>-0.335732562420456</v>
       </c>
     </row>
     <row r="416">
@@ -5574,7 +5571,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-0.367892018970997</v>
+        <v>-0.538019233343813</v>
       </c>
     </row>
     <row r="417">
@@ -5585,7 +5582,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-0.804332637611057</v>
+        <v>-0.255028252412275</v>
       </c>
     </row>
     <row r="418">
@@ -5596,7 +5593,7 @@
         <v>16</v>
       </c>
       <c r="C418" t="n">
-        <v>-0.584641264671567</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="419">
@@ -5607,7 +5604,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-0.533966505538854</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="420">
@@ -5618,7 +5615,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.658292412841086</v>
       </c>
     </row>
     <row r="421">
@@ -5640,7 +5637,7 @@
         <v>16</v>
       </c>
       <c r="C422" t="n">
-        <v>-2.03116699993756</v>
+        <v>-0.461290268198303</v>
       </c>
     </row>
     <row r="423">
@@ -5651,7 +5648,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.485267016458055</v>
+        <v>-0.668216368933651</v>
       </c>
     </row>
     <row r="424">
@@ -5662,7 +5659,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.793251689823142</v>
       </c>
     </row>
     <row r="425">
@@ -5684,7 +5681,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-0.53653639058481</v>
+        <v>-0.605480261193652</v>
       </c>
     </row>
     <row r="427">
@@ -5706,7 +5703,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.191331740946067</v>
+        <v>-0.195873415529817</v>
       </c>
     </row>
     <row r="429">
@@ -5717,7 +5714,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.361014761265987</v>
+        <v>-0.207145171228906</v>
       </c>
     </row>
     <row r="430">
@@ -5739,7 +5736,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.208673467210714</v>
       </c>
     </row>
     <row r="432">
@@ -5750,7 +5747,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.143038918081872</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="433">
@@ -5761,7 +5758,7 @@
         <v>16</v>
       </c>
       <c r="C433" t="n">
-        <v>-0.495472963112473</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="434">
@@ -5772,7 +5769,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.210399769762622</v>
+        <v>-0.185346967444944</v>
       </c>
     </row>
     <row r="435">
@@ -5783,7 +5780,7 @@
         <v>16</v>
       </c>
       <c r="C435" t="n">
-        <v>-0.163641239796821</v>
+        <v>-0.43414772420243</v>
       </c>
     </row>
     <row r="436">
@@ -5794,7 +5791,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.435396655797018</v>
+        <v>-3.21171904673829</v>
       </c>
     </row>
     <row r="437">
@@ -5816,7 +5813,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.771398445389246</v>
+        <v>-0.705289294366955</v>
       </c>
     </row>
     <row r="439">
@@ -5827,7 +5824,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.211660775311638</v>
+        <v>-2.38231772533251</v>
       </c>
     </row>
     <row r="440">
@@ -5838,7 +5835,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.756501221140947</v>
       </c>
     </row>
     <row r="441">
@@ -5849,7 +5846,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-1.34188005593756</v>
+        <v>-0.971962081491574</v>
       </c>
     </row>
     <row r="442">
@@ -5860,7 +5857,7 @@
         <v>16</v>
       </c>
       <c r="C442" t="n">
-        <v>-0.432679363381271</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="443">
@@ -5882,7 +5879,7 @@
         <v>16</v>
       </c>
       <c r="C444" t="n">
-        <v>-0.387221412141464</v>
+        <v>-0.631882681693175</v>
       </c>
     </row>
     <row r="445">
@@ -5893,7 +5890,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-1.0261389502859</v>
+        <v>-0.697039229535032</v>
       </c>
     </row>
     <row r="446">
@@ -5904,7 +5901,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.154178667927694</v>
+        <v>-0.18790077370582</v>
       </c>
     </row>
     <row r="447">
@@ -5915,7 +5912,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.636302154054041</v>
       </c>
     </row>
     <row r="448">
@@ -5937,7 +5934,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.455563726053409</v>
+        <v>-0.642311425954518</v>
       </c>
     </row>
     <row r="450">
@@ -5948,7 +5945,7 @@
         <v>16</v>
       </c>
       <c r="C450" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.61914025357113</v>
       </c>
     </row>
     <row r="451">
@@ -5959,7 +5956,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.323465188099153</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="452">
@@ -5970,7 +5967,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.252750522966168</v>
+        <v>-0.919876847860997</v>
       </c>
     </row>
     <row r="453">
@@ -5981,7 +5978,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-1.60470699097504</v>
+        <v>-1.32458562581593</v>
       </c>
     </row>
     <row r="454">
@@ -5992,7 +5989,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>-0.264379793665801</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="455">
@@ -6003,7 +6000,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.258570558664028</v>
+        <v>-0.545803976168835</v>
       </c>
     </row>
     <row r="456">
@@ -6014,7 +6011,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.418231308178829</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="457">
@@ -6036,7 +6033,7 @@
         <v>16</v>
       </c>
       <c r="C458" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.846074876253974</v>
       </c>
     </row>
     <row r="459">
@@ -6047,7 +6044,7 @@
         <v>16</v>
       </c>
       <c r="C459" t="n">
-        <v>-0.333544763977028</v>
+        <v>-0.339623640309688</v>
       </c>
     </row>
     <row r="460">
@@ -6058,7 +6055,7 @@
         <v>16</v>
       </c>
       <c r="C460" t="n">
-        <v>-0.343574353383333</v>
+        <v>-0.329340848632415</v>
       </c>
     </row>
     <row r="461">
@@ -6069,7 +6066,7 @@
         <v>16</v>
       </c>
       <c r="C461" t="n">
-        <v>-0.356723754753926</v>
+        <v>-0.664055871487753</v>
       </c>
     </row>
     <row r="462">
@@ -6091,7 +6088,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.207440734794438</v>
+        <v>-0.474411961626596</v>
       </c>
     </row>
     <row r="464">
@@ -6102,7 +6099,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.908786948449482</v>
+        <v>-0.580151305455774</v>
       </c>
     </row>
     <row r="465">
@@ -6113,7 +6110,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.475223064322447</v>
+        <v>-1.45086597370549</v>
       </c>
     </row>
     <row r="466">
@@ -6124,7 +6121,7 @@
         <v>16</v>
       </c>
       <c r="C466" t="n">
-        <v>-0.711373435474203</v>
+        <v>-0.740065774913752</v>
       </c>
     </row>
     <row r="467">
@@ -6135,7 +6132,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-2.24232265983993</v>
+        <v>-2.86774220935386</v>
       </c>
     </row>
     <row r="468">
@@ -6146,7 +6143,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.45888238775192</v>
+        <v>-0.191648867188555</v>
       </c>
     </row>
     <row r="469">
@@ -6157,7 +6154,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>-0.197794730332328</v>
+        <v>-1.52636038149095</v>
       </c>
     </row>
     <row r="470">
@@ -6168,7 +6165,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.92718734454224</v>
       </c>
     </row>
     <row r="471">
@@ -6179,7 +6176,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.446060608129316</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="472">
@@ -6201,7 +6198,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.86810345188999</v>
       </c>
     </row>
     <row r="474">
@@ -6212,7 +6209,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.77280556727911</v>
+        <v>-0.723943671862484</v>
       </c>
     </row>
     <row r="475">
@@ -6256,7 +6253,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-0.26269629808603</v>
+        <v>-0.287644988490357</v>
       </c>
     </row>
     <row r="479">
@@ -6267,7 +6264,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.378918966222961</v>
+        <v>-0.498246479006873</v>
       </c>
     </row>
     <row r="480">
@@ -6289,7 +6286,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>-0.176967715401855</v>
+        <v>-3.31141060044202</v>
       </c>
     </row>
     <row r="482">
@@ -6300,7 +6297,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.35356791450883</v>
       </c>
     </row>
     <row r="483">
@@ -6311,7 +6308,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-0.478475748736767</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="484">
@@ -6322,7 +6319,7 @@
         <v>16</v>
       </c>
       <c r="C484" t="n">
-        <v>-0.289671811077796</v>
+        <v>-0.501832263389062</v>
       </c>
     </row>
     <row r="485">
@@ -6333,7 +6330,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.464529679033244</v>
       </c>
     </row>
     <row r="486">
@@ -6355,7 +6352,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.798898491791734</v>
+        <v>-0.395593944321908</v>
       </c>
     </row>
     <row r="488">
@@ -6366,7 +6363,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.23246643055511</v>
+        <v>-0.446728109939946</v>
       </c>
     </row>
     <row r="489">
@@ -6377,7 +6374,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>-0.504901752956625</v>
+        <v>-0.181925851399894</v>
       </c>
     </row>
     <row r="490">
@@ -6388,7 +6385,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.266456870918919</v>
+        <v>-0.184769650569921</v>
       </c>
     </row>
     <row r="491">
@@ -6399,7 +6396,7 @@
         <v>16</v>
       </c>
       <c r="C491" t="n">
-        <v>-0.633006067163975</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="492">
@@ -6410,7 +6407,7 @@
         <v>16</v>
       </c>
       <c r="C492" t="n">
-        <v>-0.515954623701548</v>
+        <v>-0.487696804139748</v>
       </c>
     </row>
     <row r="493">
@@ -6421,7 +6418,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-2.28170306028296</v>
+        <v>-0.710317153033655</v>
       </c>
     </row>
     <row r="494">
@@ -6432,7 +6429,7 @@
         <v>16</v>
       </c>
       <c r="C494" t="n">
-        <v>-0.273802820808564</v>
+        <v>-0.457589697993811</v>
       </c>
     </row>
     <row r="495">
@@ -6443,7 +6440,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.190828772739607</v>
+        <v>-0.283821810260251</v>
       </c>
     </row>
     <row r="496">
@@ -6454,7 +6451,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>-0.0547376288651977</v>
+        <v>-2.56929500343459</v>
       </c>
     </row>
     <row r="497">
@@ -6465,7 +6462,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>0.471928748726851</v>
+        <v>-0.206509471402719</v>
       </c>
     </row>
     <row r="498">
@@ -6476,7 +6473,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.837502768438632</v>
+        <v>-1.31832374933491</v>
       </c>
     </row>
     <row r="499">
@@ -6487,7 +6484,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>-0.189356956971203</v>
+        <v>-0.146423420662078</v>
       </c>
     </row>
     <row r="500">
@@ -6498,7 +6495,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>-0.682296027167965</v>
+        <v>-0.364561110011996</v>
       </c>
     </row>
     <row r="501">
@@ -6509,7 +6506,7 @@
         <v>16</v>
       </c>
       <c r="C501" t="n">
-        <v>-0.390745869665408</v>
+        <v>-0.71671449874062</v>
       </c>
     </row>
     <row r="502">
@@ -6520,7 +6517,7 @@
         <v>16</v>
       </c>
       <c r="C502" t="n">
-        <v>-0.251989250044396</v>
+        <v>-1.97836538850647</v>
       </c>
     </row>
     <row r="503">
@@ -6531,7 +6528,7 @@
         <v>16</v>
       </c>
       <c r="C503" t="n">
-        <v>-0.593158842668577</v>
+        <v>-0.67874250358695</v>
       </c>
     </row>
     <row r="504">
@@ -6542,7 +6539,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.207662675404389</v>
       </c>
     </row>
     <row r="505">
@@ -6564,7 +6561,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.303354330363725</v>
+        <v>-0.241691550109935</v>
       </c>
     </row>
     <row r="507">
@@ -6575,7 +6572,7 @@
         <v>16</v>
       </c>
       <c r="C507" t="n">
-        <v>-0.634137242955258</v>
+        <v>-0.36572301591575</v>
       </c>
     </row>
     <row r="508">
@@ -6586,7 +6583,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.727144803150279</v>
+        <v>-0.43192755216507</v>
       </c>
     </row>
     <row r="509">
@@ -6597,7 +6594,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.697797934121902</v>
       </c>
     </row>
     <row r="510">
@@ -6608,7 +6605,7 @@
         <v>16</v>
       </c>
       <c r="C510" t="n">
-        <v>-0.375545136210018</v>
+        <v>0.41344722746962</v>
       </c>
     </row>
     <row r="511">
@@ -6630,7 +6627,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.93339806115468</v>
+        <v>-0.244651769828648</v>
       </c>
     </row>
     <row r="513">
@@ -6641,7 +6638,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.945117979624782</v>
+        <v>-0.973887595118917</v>
       </c>
     </row>
     <row r="514">
@@ -6652,7 +6649,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-0.354725107404119</v>
+        <v>-0.911954519249945</v>
       </c>
     </row>
     <row r="515">
@@ -6663,7 +6660,7 @@
         <v>16</v>
       </c>
       <c r="C515" t="n">
-        <v>-0.283748959934778</v>
+        <v>-0.318038266020868</v>
       </c>
     </row>
     <row r="516">
@@ -6674,7 +6671,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.351369304159568</v>
       </c>
     </row>
     <row r="517">
@@ -6685,7 +6682,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.316858490876329</v>
+        <v>-0.229438406334347</v>
       </c>
     </row>
     <row r="518">
@@ -6696,7 +6693,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-0.215416077762759</v>
+        <v>-0.748182530671897</v>
       </c>
     </row>
     <row r="519">
@@ -6718,7 +6715,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.216427917707918</v>
+        <v>-0.536392527123291</v>
       </c>
     </row>
     <row r="521">
@@ -6740,7 +6737,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.546633682457031</v>
       </c>
     </row>
     <row r="523">
@@ -6751,7 +6748,7 @@
         <v>16</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.0558131166562073</v>
+        <v>-2.50414204700658</v>
       </c>
     </row>
     <row r="524">
@@ -6762,7 +6759,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>-0.82463324283446</v>
+        <v>-0.308741555767025</v>
       </c>
     </row>
     <row r="525">
@@ -6773,7 +6770,7 @@
         <v>16</v>
       </c>
       <c r="C525" t="n">
-        <v>-0.198460044972404</v>
+        <v>-0.70348187003814</v>
       </c>
     </row>
     <row r="526">
@@ -6784,7 +6781,7 @@
         <v>16</v>
       </c>
       <c r="C526" t="n">
-        <v>-1.32410098312423</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="527">
@@ -6806,7 +6803,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>-0.375664995799844</v>
+        <v>-0.734828218832057</v>
       </c>
     </row>
     <row r="529">
@@ -6817,7 +6814,7 @@
         <v>16</v>
       </c>
       <c r="C529" t="n">
-        <v>-0.702694758243256</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="530">
@@ -6828,7 +6825,7 @@
         <v>16</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.394706309712155</v>
+        <v>-0.569455766257751</v>
       </c>
     </row>
     <row r="531">
@@ -6839,7 +6836,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-0.159763313609467</v>
+        <v>-4.0167036164105</v>
       </c>
     </row>
     <row r="532">
@@ -6850,7 +6847,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.410297471548717</v>
+        <v>-0.2085833852687</v>
       </c>
     </row>
     <row r="533">
@@ -6861,7 +6858,7 @@
         <v>16</v>
       </c>
       <c r="C533" t="n">
-        <v>-1.03115971964712</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="534">
@@ -6872,7 +6869,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.134101429546264</v>
+        <v>-0.414787429953331</v>
       </c>
     </row>
     <row r="535">
@@ -6883,7 +6880,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.20179208306086</v>
+        <v>-0.206970759895807</v>
       </c>
     </row>
     <row r="536">
@@ -6894,7 +6891,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.915138495818615</v>
+        <v>-1.22012550446712</v>
       </c>
     </row>
     <row r="537">
@@ -6905,7 +6902,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>0.834888074977812</v>
+        <v>0.942810616455228</v>
       </c>
     </row>
     <row r="538">
@@ -6916,7 +6913,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>-0.281669677856041</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="539">
@@ -6927,7 +6924,7 @@
         <v>16</v>
       </c>
       <c r="C539" t="n">
-        <v>-0.160841946193385</v>
+        <v>-0.987866659756481</v>
       </c>
     </row>
     <row r="540">
@@ -6938,7 +6935,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.553895179415419</v>
+        <v>-0.889610650769049</v>
       </c>
     </row>
     <row r="541">
@@ -6949,7 +6946,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.170034458973876</v>
+        <v>-1.83398685388938</v>
       </c>
     </row>
     <row r="542">
@@ -6982,7 +6979,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.78826754724624</v>
       </c>
     </row>
     <row r="545">
@@ -6993,7 +6990,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.596364071587676</v>
+        <v>-0.621135185220551</v>
       </c>
     </row>
     <row r="546">
@@ -7004,7 +7001,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.0794258308601132</v>
+        <v>-0.148244422541861</v>
       </c>
     </row>
     <row r="547">
@@ -7026,7 +7023,7 @@
         <v>16</v>
       </c>
       <c r="C548" t="n">
-        <v>-1.23205317161833</v>
+        <v>-0.51936326090657</v>
       </c>
     </row>
     <row r="549">
@@ -7037,7 +7034,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>0.157150972439656</v>
+        <v>-0.0602213006535042</v>
       </c>
     </row>
     <row r="550">
@@ -7048,7 +7045,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.301918107264513</v>
+        <v>-0.468120117612959</v>
       </c>
     </row>
     <row r="551">
@@ -7059,7 +7056,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-1.07686545123651</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="552">
@@ -7070,7 +7067,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.712697280200949</v>
+        <v>-1.33732918556335</v>
       </c>
     </row>
     <row r="553">
@@ -7081,7 +7078,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.997501298122052</v>
+        <v>-0.630278233817581</v>
       </c>
     </row>
     <row r="554">
@@ -7103,7 +7100,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.58522870232815</v>
+        <v>-0.209005348560537</v>
       </c>
     </row>
     <row r="556">
@@ -7114,7 +7111,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>-2.15964328751697</v>
+        <v>0.45451252579261</v>
       </c>
     </row>
     <row r="557">
@@ -7125,7 +7122,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.926683806902246</v>
+        <v>-0.523825041338139</v>
       </c>
     </row>
     <row r="558">
@@ -7136,7 +7133,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.235527514395035</v>
+        <v>-0.602302179711222</v>
       </c>
     </row>
     <row r="559">
@@ -7169,7 +7166,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.284566249166401</v>
+        <v>-0.481116596601431</v>
       </c>
     </row>
     <row r="562">
@@ -7180,7 +7177,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.23994365335095</v>
+        <v>-0.456490439285835</v>
       </c>
     </row>
     <row r="563">
@@ -7202,7 +7199,7 @@
         <v>16</v>
       </c>
       <c r="C564" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.765873048462532</v>
       </c>
     </row>
     <row r="565">
@@ -7213,7 +7210,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>0.12831401255405</v>
+        <v>-0.540280353565904</v>
       </c>
     </row>
     <row r="566">
@@ -7224,7 +7221,7 @@
         <v>16</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.18030413715332</v>
       </c>
     </row>
     <row r="567">
@@ -7235,7 +7232,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.48599736047833</v>
       </c>
     </row>
     <row r="568">
@@ -7246,7 +7243,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.339187000012479</v>
+        <v>-1.48801276151641</v>
       </c>
     </row>
     <row r="569">
@@ -7257,7 +7254,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.313109824480986</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="570">
@@ -7279,7 +7276,7 @@
         <v>16</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.256554335709725</v>
+        <v>-0.189239611242912</v>
       </c>
     </row>
     <row r="572">
@@ -7290,7 +7287,7 @@
         <v>16</v>
       </c>
       <c r="C572" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.188140241116167</v>
       </c>
     </row>
     <row r="573">
@@ -7301,7 +7298,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.481084142021353</v>
+        <v>-0.501076314935622</v>
       </c>
     </row>
     <row r="574">
@@ -7312,7 +7309,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.174718638011097</v>
+        <v>-2.26020265027712</v>
       </c>
     </row>
     <row r="575">
@@ -7323,7 +7320,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>0.761129333226281</v>
+        <v>0.704062124603862</v>
       </c>
     </row>
     <row r="576">
@@ -7334,7 +7331,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.0702836240153806</v>
+        <v>-2.78922022525526</v>
       </c>
     </row>
     <row r="577">
@@ -7345,7 +7342,7 @@
         <v>16</v>
       </c>
       <c r="C577" t="n">
-        <v>-0.24389187245243</v>
+        <v>-0.44651653031691</v>
       </c>
     </row>
     <row r="578">
@@ -7356,7 +7353,7 @@
         <v>16</v>
       </c>
       <c r="C578" t="n">
-        <v>-0.602410222393022</v>
+        <v>-0.936085995177377</v>
       </c>
     </row>
     <row r="579">
@@ -7367,7 +7364,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-0.983436120832687</v>
+        <v>-0.903907304801232</v>
       </c>
     </row>
     <row r="580">
@@ -7378,7 +7375,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>-0.429154735350705</v>
+        <v>-0.577845177636926</v>
       </c>
     </row>
     <row r="581">
@@ -7389,7 +7386,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.24361486016484</v>
+        <v>0.294373034876229</v>
       </c>
     </row>
     <row r="582">
@@ -7400,7 +7397,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.707752297247956</v>
+        <v>-0.601630042730084</v>
       </c>
     </row>
     <row r="583">
@@ -7411,7 +7408,7 @@
         <v>16</v>
       </c>
       <c r="C583" t="n">
-        <v>-0.168757099606928</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="584">
@@ -7433,7 +7430,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.777384021777056</v>
+        <v>0.0150233609478342</v>
       </c>
     </row>
     <row r="586">
@@ -7444,7 +7441,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.891573384738272</v>
+        <v>-0.0252090970082239</v>
       </c>
     </row>
     <row r="587">
@@ -7455,7 +7452,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.186340407332546</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="588">
@@ -7466,7 +7463,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.84510849004932</v>
+        <v>-0.552605241984045</v>
       </c>
     </row>
     <row r="589">
@@ -7477,7 +7474,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.0329414224474931</v>
+        <v>-0.116926235563737</v>
       </c>
     </row>
     <row r="590">
@@ -7488,7 +7485,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-0.184712270640092</v>
+        <v>-0.177211792823533</v>
       </c>
     </row>
     <row r="591">
@@ -7499,7 +7496,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.452695320866433</v>
       </c>
     </row>
     <row r="592">
@@ -7510,7 +7507,7 @@
         <v>16</v>
       </c>
       <c r="C592" t="n">
-        <v>-0.237736589017648</v>
+        <v>-0.581808191375587</v>
       </c>
     </row>
     <row r="593">
@@ -7521,7 +7518,7 @@
         <v>16</v>
       </c>
       <c r="C593" t="n">
-        <v>-0.98763762111627</v>
+        <v>-0.859681421517856</v>
       </c>
     </row>
     <row r="594">
@@ -7532,7 +7529,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-0.495742891527848</v>
+        <v>-0.825418143023606</v>
       </c>
     </row>
     <row r="595">
@@ -7543,7 +7540,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>-0.478002316312915</v>
+        <v>-1.67033854362912</v>
       </c>
     </row>
     <row r="596">
@@ -7554,7 +7551,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.335007828768407</v>
       </c>
     </row>
     <row r="597">
@@ -7565,7 +7562,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-3.0994743961658</v>
+        <v>-0.772800613068134</v>
       </c>
     </row>
     <row r="598">
@@ -7576,7 +7573,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-1.45710644518058</v>
+        <v>-2.42828332127059</v>
       </c>
     </row>
     <row r="599">
@@ -7587,7 +7584,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-0.400929799309929</v>
+        <v>-0.396489013302389</v>
       </c>
     </row>
     <row r="600">
@@ -7598,7 +7595,7 @@
         <v>16</v>
       </c>
       <c r="C600" t="n">
-        <v>0.487145369228727</v>
+        <v>-0.465374870673693</v>
       </c>
     </row>
     <row r="601">
@@ -7609,7 +7606,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.760892006213855</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="602">
@@ -7631,7 +7628,7 @@
         <v>16</v>
       </c>
       <c r="C603" t="n">
-        <v>-0.318806728958699</v>
+        <v>-3.8944707075264</v>
       </c>
     </row>
     <row r="604">
@@ -7642,7 +7639,7 @@
         <v>16</v>
       </c>
       <c r="C604" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.833810773427925</v>
       </c>
     </row>
     <row r="605">
@@ -7653,7 +7650,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.521602636702968</v>
+        <v>-0.752521544308401</v>
       </c>
     </row>
     <row r="606">
@@ -7686,7 +7683,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-1.94366469654036</v>
+        <v>-6.00229076936716</v>
       </c>
     </row>
     <row r="609">
@@ -7708,7 +7705,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.454080756395847</v>
+        <v>-0.484057969506596</v>
       </c>
     </row>
     <row r="611">
@@ -7719,7 +7716,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-1.21841278522865</v>
+        <v>-1.02234169766632</v>
       </c>
     </row>
     <row r="612">
@@ -7730,7 +7727,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.126990948153119</v>
       </c>
     </row>
     <row r="613">
@@ -7741,7 +7738,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.507727904179045</v>
+        <v>-0.475075714912913</v>
       </c>
     </row>
     <row r="614">
@@ -7752,7 +7749,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.268307101490679</v>
+        <v>-0.1716557020189</v>
       </c>
     </row>
     <row r="615">
@@ -7763,7 +7760,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.22411088940406</v>
+        <v>-0.674672179622259</v>
       </c>
     </row>
     <row r="616">
@@ -7785,7 +7782,7 @@
         <v>16</v>
       </c>
       <c r="C617" t="n">
-        <v>-1.26623039013586</v>
+        <v>-0.915668242071087</v>
       </c>
     </row>
     <row r="618">
@@ -7796,7 +7793,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.420680836292226</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="619">
@@ -7818,7 +7815,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.18606549631075</v>
       </c>
     </row>
     <row r="621">
@@ -7829,7 +7826,7 @@
         <v>16</v>
       </c>
       <c r="C621" t="n">
-        <v>-0.158796218821556</v>
+        <v>-0.302464944001944</v>
       </c>
     </row>
     <row r="622">
@@ -7840,7 +7837,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-0.278658326775856</v>
+        <v>-0.304033018955418</v>
       </c>
     </row>
     <row r="623">
@@ -7851,7 +7848,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.607217307747017</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="624">
@@ -7862,7 +7859,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>-0.999054675828654</v>
+        <v>-0.177046646476637</v>
       </c>
     </row>
     <row r="625">
@@ -7873,7 +7870,7 @@
         <v>16</v>
       </c>
       <c r="C625" t="n">
-        <v>-0.575173690023828</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="626">
@@ -7884,7 +7881,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.364675861353554</v>
+        <v>-0.880110925897839</v>
       </c>
     </row>
     <row r="627">
@@ -7895,7 +7892,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.268313194929395</v>
+        <v>-0.977400464011808</v>
       </c>
     </row>
     <row r="628">
@@ -7906,7 +7903,7 @@
         <v>16</v>
       </c>
       <c r="C628" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.585882628341735</v>
       </c>
     </row>
     <row r="629">
@@ -7917,7 +7914,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.307564194074221</v>
       </c>
     </row>
     <row r="630">
@@ -7928,7 +7925,7 @@
         <v>16</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.896436568850987</v>
       </c>
     </row>
     <row r="631">
@@ -7950,7 +7947,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.803956875730071</v>
       </c>
     </row>
     <row r="633">
@@ -7961,7 +7958,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.864652197621428</v>
+        <v>-0.228023429279</v>
       </c>
     </row>
     <row r="634">
@@ -7994,7 +7991,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.164955689894965</v>
+        <v>-0.173542725435065</v>
       </c>
     </row>
     <row r="637">
@@ -8005,7 +8002,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.214962730349106</v>
       </c>
     </row>
     <row r="638">
@@ -8016,7 +8013,7 @@
         <v>16</v>
       </c>
       <c r="C638" t="n">
-        <v>-0.256586071862953</v>
+        <v>-0.0478815351475326</v>
       </c>
     </row>
     <row r="639">
@@ -8027,7 +8024,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.417394638320902</v>
+        <v>-0.791842665590845</v>
       </c>
     </row>
     <row r="640">
@@ -8038,7 +8035,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.65219192059587</v>
+        <v>-1.00549319368542</v>
       </c>
     </row>
     <row r="641">
@@ -8093,7 +8090,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-2.06922192037591</v>
+        <v>-0.905596593046376</v>
       </c>
     </row>
     <row r="646">
@@ -8115,7 +8112,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>-0.307090682235946</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="648">
@@ -8126,7 +8123,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>-1.41676529481796</v>
+        <v>-2.03020816983987</v>
       </c>
     </row>
     <row r="649">
@@ -8137,7 +8134,7 @@
         <v>16</v>
       </c>
       <c r="C649" t="n">
-        <v>-0.585702586193557</v>
+        <v>-0.226176962991604</v>
       </c>
     </row>
     <row r="650">
@@ -8148,7 +8145,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>-2.31574168974224</v>
+        <v>-0.250079654331463</v>
       </c>
     </row>
     <row r="651">
@@ -8159,7 +8156,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>0.0168520444428719</v>
+        <v>0.496591530995572</v>
       </c>
     </row>
     <row r="652">
@@ -8170,7 +8167,7 @@
         <v>16</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.161549777511636</v>
+        <v>-0.332565149797415</v>
       </c>
     </row>
     <row r="653">
@@ -8181,7 +8178,7 @@
         <v>16</v>
       </c>
       <c r="C653" t="n">
-        <v>-0.204668217304732</v>
+        <v>-0.154480532811856</v>
       </c>
     </row>
     <row r="654">
@@ -8192,7 +8189,7 @@
         <v>16</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.417973976741167</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="655">
@@ -8203,7 +8200,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.338532208517405</v>
       </c>
     </row>
     <row r="656">
@@ -8236,7 +8233,7 @@
         <v>16</v>
       </c>
       <c r="C658" t="n">
-        <v>0.481293734094973</v>
+        <v>-0.870781049421397</v>
       </c>
     </row>
     <row r="659">
@@ -8258,7 +8255,7 @@
         <v>16</v>
       </c>
       <c r="C660" t="n">
-        <v>-1.03425181089613</v>
+        <v>-0.0510992814047899</v>
       </c>
     </row>
     <row r="661">
@@ -8269,7 +8266,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.406265536339653</v>
+        <v>-3.83992731633144</v>
       </c>
     </row>
     <row r="662">
@@ -8280,7 +8277,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>0.551027626386779</v>
+        <v>0.42087027784726</v>
       </c>
     </row>
     <row r="663">
@@ -8291,7 +8288,7 @@
         <v>16</v>
       </c>
       <c r="C663" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.41148351123541</v>
       </c>
     </row>
     <row r="664">
@@ -8302,7 +8299,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.377026804804959</v>
+        <v>-0.458452824106466</v>
       </c>
     </row>
     <row r="665">
@@ -8313,7 +8310,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.503456391682274</v>
+        <v>-0.5670775301339</v>
       </c>
     </row>
     <row r="666">
@@ -8324,7 +8321,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.283587938828379</v>
+        <v>-1.38064354781479</v>
       </c>
     </row>
     <row r="667">
@@ -8346,7 +8343,7 @@
         <v>16</v>
       </c>
       <c r="C668" t="n">
-        <v>-1.58286396261146</v>
+        <v>-0.413150375945698</v>
       </c>
     </row>
     <row r="669">
@@ -8368,7 +8365,7 @@
         <v>16</v>
       </c>
       <c r="C670" t="n">
-        <v>-0.246585950273704</v>
+        <v>-0.452024734447052</v>
       </c>
     </row>
     <row r="671">
@@ -8379,7 +8376,7 @@
         <v>16</v>
       </c>
       <c r="C671" t="n">
-        <v>-0.563869490754592</v>
+        <v>-0.780753303881001</v>
       </c>
     </row>
     <row r="672">
@@ -8390,7 +8387,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.709088432131488</v>
+        <v>-0.849863219649359</v>
       </c>
     </row>
     <row r="673">
@@ -8412,7 +8409,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.815291663960299</v>
       </c>
     </row>
     <row r="675">
@@ -8423,7 +8420,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.707913581105925</v>
+        <v>-4.60442652769129</v>
       </c>
     </row>
     <row r="676">
@@ -8445,7 +8442,7 @@
         <v>16</v>
       </c>
       <c r="C677" t="n">
-        <v>-0.0571215187829999</v>
+        <v>-0.176939522263135</v>
       </c>
     </row>
     <row r="678">
@@ -8456,7 +8453,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-3.66871082681405</v>
+        <v>-0.0668733797186141</v>
       </c>
     </row>
     <row r="679">
@@ -8467,7 +8464,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.461555818289835</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="680">
@@ -8511,7 +8508,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-0.121847556254894</v>
+        <v>-0.189521650498886</v>
       </c>
     </row>
     <row r="684">
@@ -8522,7 +8519,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-1.22566619832344</v>
+        <v>-1.99104033200969</v>
       </c>
     </row>
     <row r="685">
@@ -8533,7 +8530,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>-0.433896408300965</v>
+        <v>-1.03432136189086</v>
       </c>
     </row>
     <row r="686">
@@ -8544,7 +8541,7 @@
         <v>16</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.188813624353263</v>
+        <v>-0.189881581336179</v>
       </c>
     </row>
     <row r="687">
@@ -8566,7 +8563,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>0.245820179028336</v>
+        <v>-0.667037910123617</v>
       </c>
     </row>
     <row r="689">
@@ -8577,7 +8574,7 @@
         <v>16</v>
       </c>
       <c r="C689" t="n">
-        <v>-0.46279898409895</v>
+        <v>-0.546428127197374</v>
       </c>
     </row>
     <row r="690">
@@ -8588,7 +8585,7 @@
         <v>16</v>
       </c>
       <c r="C690" t="n">
-        <v>-0.0726563359788324</v>
+        <v>0.059838881154743</v>
       </c>
     </row>
     <row r="691">
@@ -8599,7 +8596,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.233777209100647</v>
+        <v>-0.212633807206263</v>
       </c>
     </row>
     <row r="692">
@@ -8610,7 +8607,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.218896945534528</v>
       </c>
     </row>
     <row r="693">
@@ -8621,7 +8618,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-0.578536463239455</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="694">
@@ -8632,7 +8629,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>-0.772637712049334</v>
+        <v>-0.754234710601053</v>
       </c>
     </row>
     <row r="695">
@@ -8643,7 +8640,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>0.238506673843042</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="696">
@@ -8654,7 +8651,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>0.78145850257842</v>
+        <v>0.735713773136038</v>
       </c>
     </row>
     <row r="697">
@@ -8665,7 +8662,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.497082359476343</v>
       </c>
     </row>
     <row r="698">
@@ -8676,7 +8673,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.170882569337028</v>
       </c>
     </row>
     <row r="699">
@@ -8687,7 +8684,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.330830776892291</v>
+        <v>-0.362611779669395</v>
       </c>
     </row>
     <row r="700">
@@ -8698,7 +8695,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.05538856499762</v>
       </c>
     </row>
     <row r="701">
@@ -8720,7 +8717,7 @@
         <v>16</v>
       </c>
       <c r="C702" t="n">
-        <v>-0.183640057687575</v>
+        <v>-0.875748217269703</v>
       </c>
     </row>
     <row r="703">
@@ -8753,7 +8750,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.308601341916756</v>
+        <v>-0.266343507129169</v>
       </c>
     </row>
     <row r="706">
@@ -8764,7 +8761,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-1.34728389571611</v>
+        <v>-0.188486181089764</v>
       </c>
     </row>
     <row r="707">
@@ -8775,7 +8772,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.226165445631987</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="708">
@@ -8786,7 +8783,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-0.420910501134368</v>
+        <v>-0.609839681693643</v>
       </c>
     </row>
     <row r="709">
@@ -8797,7 +8794,7 @@
         <v>16</v>
       </c>
       <c r="C709" t="n">
-        <v>-0.442900063503324</v>
+        <v>-0.196793282371842</v>
       </c>
     </row>
     <row r="710">
@@ -8808,7 +8805,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.410859942638575</v>
       </c>
     </row>
     <row r="711">
@@ -8819,7 +8816,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.735956150409587</v>
+        <v>-0.162759351077828</v>
       </c>
     </row>
     <row r="712">
@@ -8841,7 +8838,7 @@
         <v>16</v>
       </c>
       <c r="C713" t="n">
-        <v>-0.7747219399846</v>
+        <v>-0.271624696076101</v>
       </c>
     </row>
     <row r="714">
@@ -8852,7 +8849,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.4198675218318</v>
       </c>
     </row>
     <row r="715">
@@ -8863,7 +8860,7 @@
         <v>16</v>
       </c>
       <c r="C715" t="n">
-        <v>-0.695495293764687</v>
+        <v>-0.796751340054931</v>
       </c>
     </row>
     <row r="716">
@@ -8874,7 +8871,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.40621959950614</v>
       </c>
     </row>
     <row r="717">
@@ -8885,7 +8882,7 @@
         <v>16</v>
       </c>
       <c r="C717" t="n">
-        <v>-0.602420116527019</v>
+        <v>0.202495501510388</v>
       </c>
     </row>
     <row r="718">
@@ -8896,7 +8893,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.129693177424431</v>
+        <v>-0.0380004857802192</v>
       </c>
     </row>
     <row r="719">
@@ -8907,7 +8904,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>-0.0779237379130855</v>
+        <v>-0.096051946204091</v>
       </c>
     </row>
     <row r="720">
@@ -8918,7 +8915,7 @@
         <v>16</v>
       </c>
       <c r="C720" t="n">
-        <v>-0.193544289815721</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="721">
@@ -8929,7 +8926,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>-0.479608064820579</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="722">
@@ -8940,7 +8937,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.928689530478132</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="723">
@@ -8951,7 +8948,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.604594999029349</v>
+        <v>-0.195606527706456</v>
       </c>
     </row>
     <row r="724">
@@ -8962,7 +8959,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.406328632026083</v>
       </c>
     </row>
     <row r="725">
@@ -8973,7 +8970,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.999267524952581</v>
+        <v>-0.966629990889375</v>
       </c>
     </row>
     <row r="726">
@@ -9006,7 +9003,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.856219743824398</v>
+        <v>-0.335672783533721</v>
       </c>
     </row>
     <row r="729">
@@ -9017,7 +9014,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>0.158885418992147</v>
+        <v>-0.0228657572421556</v>
       </c>
     </row>
     <row r="730">
@@ -9028,7 +9025,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.168007197020466</v>
+        <v>-0.776946416200363</v>
       </c>
     </row>
     <row r="731">
@@ -9039,7 +9036,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.187220178208445</v>
+        <v>-3.56207064221983</v>
       </c>
     </row>
     <row r="732">
@@ -9050,7 +9047,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.773346379869417</v>
       </c>
     </row>
     <row r="733">
@@ -9061,7 +9058,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.103682173417786</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="734">
@@ -9072,7 +9069,7 @@
         <v>16</v>
       </c>
       <c r="C734" t="n">
-        <v>-0.0862191417950866</v>
+        <v>-0.0749717573819089</v>
       </c>
     </row>
     <row r="735">
@@ -9105,7 +9102,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.123576702819912</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="738">
@@ -9116,7 +9113,7 @@
         <v>16</v>
       </c>
       <c r="C738" t="n">
-        <v>-0.567018668394002</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="739">
@@ -9138,7 +9135,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.202564091851018</v>
+        <v>-0.328167314496036</v>
       </c>
     </row>
     <row r="741">
@@ -9149,7 +9146,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.229453120534216</v>
+        <v>-0.312334646397396</v>
       </c>
     </row>
     <row r="742">
@@ -9160,7 +9157,7 @@
         <v>16</v>
       </c>
       <c r="C742" t="n">
-        <v>-0.183552134035489</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="743">
@@ -9171,7 +9168,7 @@
         <v>16</v>
       </c>
       <c r="C743" t="n">
-        <v>-0.335589343361626</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="744">
@@ -9193,7 +9190,7 @@
         <v>16</v>
       </c>
       <c r="C745" t="n">
-        <v>-0.595003426698949</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="746">
@@ -9204,7 +9201,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.530988512725798</v>
+        <v>-0.772992976463862</v>
       </c>
     </row>
     <row r="747">
@@ -9215,7 +9212,7 @@
         <v>16</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.840676878246167</v>
       </c>
     </row>
     <row r="748">
@@ -9237,7 +9234,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.367665754938256</v>
       </c>
     </row>
     <row r="750">
@@ -9248,7 +9245,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.241194117130652</v>
       </c>
     </row>
     <row r="751">
@@ -9259,7 +9256,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-0.215038475099398</v>
+        <v>0.203571654655559</v>
       </c>
     </row>
     <row r="752">
@@ -9270,7 +9267,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>0.373508861130244</v>
+        <v>-0.0229270088475857</v>
       </c>
     </row>
     <row r="753">
@@ -9281,7 +9278,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.139956730316304</v>
+        <v>-0.18207995546377</v>
       </c>
     </row>
     <row r="754">
@@ -9292,7 +9289,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>-0.683129438730017</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="755">
@@ -9314,7 +9311,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.171288000189662</v>
+        <v>-0.405642370663511</v>
       </c>
     </row>
     <row r="757">
@@ -9336,7 +9333,7 @@
         <v>16</v>
       </c>
       <c r="C758" t="n">
-        <v>-0.29838091780154</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="759">
@@ -9347,7 +9344,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.448100465954082</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="760">
@@ -9358,7 +9355,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.222084971713968</v>
+        <v>0.539111431554527</v>
       </c>
     </row>
     <row r="761">
@@ -9369,7 +9366,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.640293956669517</v>
       </c>
     </row>
     <row r="762">
@@ -9413,7 +9410,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.20473927673716</v>
       </c>
     </row>
     <row r="766">
@@ -9424,7 +9421,7 @@
         <v>16</v>
       </c>
       <c r="C766" t="n">
-        <v>-0.11347564387127</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="767">
@@ -9435,7 +9432,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.266646260811576</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="768">
@@ -9446,7 +9443,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.432443795834542</v>
+        <v>-0.614681903012785</v>
       </c>
     </row>
     <row r="769">
@@ -9457,7 +9454,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.24435314451092</v>
+        <v>-0.333234492956639</v>
       </c>
     </row>
     <row r="770">
@@ -9468,7 +9465,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.344885017870261</v>
+        <v>-0.393778070116289</v>
       </c>
     </row>
     <row r="771">
@@ -9479,7 +9476,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.292704889409794</v>
+        <v>-0.459965674661746</v>
       </c>
     </row>
     <row r="772">
@@ -9490,7 +9487,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.316597371877746</v>
+        <v>-0.504606565416531</v>
       </c>
     </row>
     <row r="773">
@@ -9501,7 +9498,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.293626272872136</v>
+        <v>0.696972219211313</v>
       </c>
     </row>
     <row r="774">
@@ -9512,7 +9509,7 @@
         <v>16</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.369452784786797</v>
+        <v>-1.68056332379004</v>
       </c>
     </row>
     <row r="775">
@@ -9523,7 +9520,7 @@
         <v>16</v>
       </c>
       <c r="C775" t="n">
-        <v>-0.226226127965373</v>
+        <v>-0.188527228833413</v>
       </c>
     </row>
     <row r="776">
@@ -9545,7 +9542,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.216324962910737</v>
+        <v>-0.762767416060632</v>
       </c>
     </row>
     <row r="778">
@@ -9600,7 +9597,7 @@
         <v>16</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.684921648770329</v>
+        <v>-0.529086951711694</v>
       </c>
     </row>
     <row r="783">
@@ -9611,7 +9608,7 @@
         <v>16</v>
       </c>
       <c r="C783" t="n">
-        <v>-1.22637877973722</v>
+        <v>-0.264134628886471</v>
       </c>
     </row>
     <row r="784">
@@ -9622,7 +9619,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>-0.43467328273968</v>
+        <v>-0.687529173227869</v>
       </c>
     </row>
     <row r="785">
@@ -9633,7 +9630,7 @@
         <v>16</v>
       </c>
       <c r="C785" t="n">
-        <v>-5.03656903707083</v>
+        <v>-0.493970875441772</v>
       </c>
     </row>
     <row r="786">
@@ -9644,7 +9641,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-0.182546488780185</v>
+        <v>-0.184639815085952</v>
       </c>
     </row>
     <row r="787">
@@ -9666,7 +9663,7 @@
         <v>16</v>
       </c>
       <c r="C788" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.398282728539915</v>
       </c>
     </row>
     <row r="789">
@@ -9677,7 +9674,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>0.18719582854976</v>
+        <v>0.391647910722352</v>
       </c>
     </row>
     <row r="790">
@@ -9688,7 +9685,7 @@
         <v>16</v>
       </c>
       <c r="C790" t="n">
-        <v>-0.186067761438898</v>
+        <v>-0.0879869956048496</v>
       </c>
     </row>
     <row r="791">
@@ -9710,7 +9707,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.426399030067409</v>
+        <v>-2.04233494063515</v>
       </c>
     </row>
     <row r="793">
@@ -9732,7 +9729,7 @@
         <v>16</v>
       </c>
       <c r="C794" t="n">
-        <v>-0.216641350329906</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="795">
@@ -9754,7 +9751,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>0.196274446906648</v>
+        <v>-1.39173302954232</v>
       </c>
     </row>
     <row r="797">
@@ -9765,7 +9762,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.442204153302077</v>
       </c>
     </row>
     <row r="798">
@@ -9776,7 +9773,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.217459350624444</v>
+        <v>-0.242011925901574</v>
       </c>
     </row>
     <row r="799">
@@ -9787,7 +9784,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.235865506616734</v>
       </c>
     </row>
     <row r="800">
@@ -9798,7 +9795,7 @@
         <v>16</v>
       </c>
       <c r="C800" t="n">
-        <v>-1.21219529637793</v>
+        <v>-0.472268697922785</v>
       </c>
     </row>
     <row r="801">
@@ -9809,7 +9806,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-0.506941419658464</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="802">
@@ -9820,7 +9817,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.793543941169116</v>
+        <v>-0.279096082221661</v>
       </c>
     </row>
     <row r="803">
@@ -9831,7 +9828,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.598168403917074</v>
+        <v>-0.261297042679293</v>
       </c>
     </row>
     <row r="804">
@@ -9842,7 +9839,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.686324000842274</v>
+        <v>-0.709386806757473</v>
       </c>
     </row>
     <row r="805">
@@ -9853,7 +9850,7 @@
         <v>16</v>
       </c>
       <c r="C805" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.682625662358371</v>
       </c>
     </row>
     <row r="806">
@@ -9864,7 +9861,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.076819136704618</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="807">
@@ -9886,7 +9883,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>0.0993079063877997</v>
+        <v>-0.0163776842140646</v>
       </c>
     </row>
     <row r="809">
@@ -9908,7 +9905,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.268610975980175</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="811">
@@ -9919,7 +9916,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.159763313609467</v>
+        <v>-4.00762865771863</v>
       </c>
     </row>
     <row r="812">
@@ -9930,7 +9927,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.231156071232433</v>
+        <v>-0.216354684531755</v>
       </c>
     </row>
     <row r="813">
@@ -9941,7 +9938,7 @@
         <v>16</v>
       </c>
       <c r="C813" t="n">
-        <v>-0.53767864786478</v>
+        <v>-0.302528142553117</v>
       </c>
     </row>
     <row r="814">
@@ -9952,7 +9949,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.592842594622607</v>
+        <v>-0.73942970853565</v>
       </c>
     </row>
     <row r="815">
@@ -9963,7 +9960,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.261769873272803</v>
+        <v>-0.522457486283712</v>
       </c>
     </row>
     <row r="816">
@@ -9974,7 +9971,7 @@
         <v>16</v>
       </c>
       <c r="C816" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.399860985307999</v>
       </c>
     </row>
     <row r="817">
@@ -9996,7 +9993,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>0.32727863915308</v>
+        <v>0.228935614875214</v>
       </c>
     </row>
     <row r="819">
@@ -10007,7 +10004,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.47875820351473</v>
       </c>
     </row>
     <row r="820">
@@ -10018,7 +10015,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.429775224889998</v>
       </c>
     </row>
     <row r="821">
@@ -10029,7 +10026,7 @@
         <v>16</v>
       </c>
       <c r="C821" t="n">
-        <v>-0.651551295686208</v>
+        <v>-0.562316817253396</v>
       </c>
     </row>
     <row r="822">
@@ -10040,7 +10037,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-1.01268240486124</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="823">
@@ -10051,7 +10048,7 @@
         <v>16</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.537498175984515</v>
+        <v>-0.676474335037507</v>
       </c>
     </row>
     <row r="824">
@@ -10062,7 +10059,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.266053559333251</v>
+        <v>-0.313816936578167</v>
       </c>
     </row>
     <row r="825">
@@ -10073,7 +10070,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-1.18611222005468</v>
+        <v>-0.585225996885119</v>
       </c>
     </row>
     <row r="826">
@@ -10084,7 +10081,7 @@
         <v>16</v>
       </c>
       <c r="C826" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.604501295994843</v>
       </c>
     </row>
     <row r="827">
@@ -10095,7 +10092,7 @@
         <v>16</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.233845594924073</v>
+        <v>-2.61406285444776</v>
       </c>
     </row>
     <row r="828">
@@ -10106,7 +10103,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.754628879813389</v>
       </c>
     </row>
     <row r="829">
@@ -10117,7 +10114,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.228334292561545</v>
+        <v>-0.258587793063912</v>
       </c>
     </row>
     <row r="830">
@@ -10128,7 +10125,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-0.77428883852171</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="831">
@@ -10139,7 +10136,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.214412940832942</v>
+        <v>-1.34594492583812</v>
       </c>
     </row>
     <row r="832">
@@ -10161,7 +10158,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.41809810225453</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="834">
@@ -10172,7 +10169,7 @@
         <v>16</v>
       </c>
       <c r="C834" t="n">
-        <v>-0.325112113079112</v>
+        <v>-0.268346456529037</v>
       </c>
     </row>
     <row r="835">
@@ -10183,7 +10180,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>0.572622159849095</v>
+        <v>-0.279417447909052</v>
       </c>
     </row>
     <row r="836">
@@ -10194,7 +10191,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.351525429049078</v>
+        <v>-0.438934936613718</v>
       </c>
     </row>
     <row r="837">
@@ -10216,7 +10213,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.325169214604539</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="839">
@@ -10238,7 +10235,7 @@
         <v>16</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.194571091243693</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="841">
@@ -10249,7 +10246,7 @@
         <v>16</v>
       </c>
       <c r="C841" t="n">
-        <v>-0.608225432913216</v>
+        <v>-0.62995344719041</v>
       </c>
     </row>
     <row r="842">
@@ -10260,7 +10257,7 @@
         <v>16</v>
       </c>
       <c r="C842" t="n">
-        <v>-0.230245739627639</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="843">
@@ -10271,7 +10268,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.148659727788536</v>
+        <v>-0.834860885110012</v>
       </c>
     </row>
     <row r="844">
@@ -10282,7 +10279,7 @@
         <v>16</v>
       </c>
       <c r="C844" t="n">
-        <v>-0.241663413066614</v>
+        <v>-0.211822801876683</v>
       </c>
     </row>
     <row r="845">
@@ -10293,7 +10290,7 @@
         <v>16</v>
       </c>
       <c r="C845" t="n">
-        <v>-0.842695743813</v>
+        <v>-0.450567389798896</v>
       </c>
     </row>
     <row r="846">
@@ -10304,7 +10301,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.869274491533885</v>
       </c>
     </row>
     <row r="847">
@@ -10315,7 +10312,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.553838579445831</v>
+        <v>-0.72221527021818</v>
       </c>
     </row>
     <row r="848">
@@ -10326,7 +10323,7 @@
         <v>16</v>
       </c>
       <c r="C848" t="n">
-        <v>-0.0801674904839429</v>
+        <v>-4.12085305346254</v>
       </c>
     </row>
     <row r="849">
@@ -10337,7 +10334,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>0.455297371869497</v>
+        <v>0.446518988208774</v>
       </c>
     </row>
     <row r="850">
@@ -10348,7 +10345,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.451881234645072</v>
+        <v>-0.201313162785877</v>
       </c>
     </row>
     <row r="851">
@@ -10359,7 +10356,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.76376479202263</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="852">
@@ -10381,7 +10378,7 @@
         <v>16</v>
       </c>
       <c r="C853" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.417945072198175</v>
       </c>
     </row>
     <row r="854">
@@ -10392,7 +10389,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-0.223497204145389</v>
+        <v>-0.391512628994705</v>
       </c>
     </row>
     <row r="855">
@@ -10403,7 +10400,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>0.505712955928894</v>
+        <v>0.525244603818606</v>
       </c>
     </row>
     <row r="856">
@@ -10414,7 +10411,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.559158307388992</v>
+        <v>-0.954847499065521</v>
       </c>
     </row>
     <row r="857">
@@ -10425,7 +10422,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.25977973482242</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="858">
@@ -10436,7 +10433,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>0.588367931191258</v>
+        <v>0.420859288701702</v>
       </c>
     </row>
     <row r="859">
@@ -10447,7 +10444,7 @@
         <v>16</v>
       </c>
       <c r="C859" t="n">
-        <v>-0.460273197174088</v>
+        <v>0.269325236337927</v>
       </c>
     </row>
     <row r="860">
@@ -10458,7 +10455,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.705169312971771</v>
       </c>
     </row>
     <row r="861">
@@ -10469,7 +10466,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.297009926486238</v>
+        <v>-0.296705434084658</v>
       </c>
     </row>
     <row r="862">
@@ -10480,7 +10477,7 @@
         <v>16</v>
       </c>
       <c r="C862" t="n">
-        <v>-0.643754070320447</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="863">
@@ -10491,7 +10488,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-4.85152699432633</v>
+        <v>-2.50468396679622</v>
       </c>
     </row>
     <row r="864">
@@ -10502,7 +10499,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.427472675870834</v>
+        <v>-1.90457760255513</v>
       </c>
     </row>
     <row r="865">
@@ -10513,7 +10510,7 @@
         <v>16</v>
       </c>
       <c r="C865" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.226628274867771</v>
       </c>
     </row>
     <row r="866">
@@ -10524,7 +10521,7 @@
         <v>16</v>
       </c>
       <c r="C866" t="n">
-        <v>0.00826849289879494</v>
+        <v>-1.06820315045764</v>
       </c>
     </row>
     <row r="867">
@@ -10535,7 +10532,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.293928007798444</v>
+        <v>-0.0784528421981652</v>
       </c>
     </row>
     <row r="868">
@@ -10546,7 +10543,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.144999731014202</v>
+        <v>-0.284562749584889</v>
       </c>
     </row>
     <row r="869">
@@ -10557,7 +10554,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.244518409142956</v>
+        <v>-0.241466413126834</v>
       </c>
     </row>
     <row r="870">
@@ -10568,7 +10565,7 @@
         <v>16</v>
       </c>
       <c r="C870" t="n">
-        <v>-0.334628112268693</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="871">
@@ -10579,7 +10576,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.291630110300175</v>
+        <v>-1.17242021928726</v>
       </c>
     </row>
     <row r="872">
@@ -10601,7 +10598,7 @@
         <v>16</v>
       </c>
       <c r="C873" t="n">
-        <v>-0.379860628740835</v>
+        <v>-0.335740276097766</v>
       </c>
     </row>
     <row r="874">
@@ -10612,7 +10609,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.380403206378859</v>
+        <v>-0.233140325869173</v>
       </c>
     </row>
     <row r="875">
@@ -10623,7 +10620,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.248274041128007</v>
+        <v>-0.215049207262196</v>
       </c>
     </row>
     <row r="876">
@@ -10634,7 +10631,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.786651801769549</v>
+        <v>-0.77353946646842</v>
       </c>
     </row>
     <row r="877">
@@ -10645,7 +10642,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.349693212550872</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="878">
@@ -10656,7 +10653,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>0.18592785767119</v>
+        <v>0.0979919851978408</v>
       </c>
     </row>
     <row r="879">
@@ -10667,7 +10664,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>0.709535973277314</v>
+        <v>-0.56983671088658</v>
       </c>
     </row>
     <row r="880">
@@ -10678,7 +10675,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.541301113235305</v>
       </c>
     </row>
     <row r="881">
@@ -10689,7 +10686,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.895498395797135</v>
       </c>
     </row>
     <row r="882">
@@ -10700,7 +10697,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.89110849191503</v>
       </c>
     </row>
     <row r="883">
@@ -10711,7 +10708,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-1.11707887037335</v>
+        <v>-0.759953590573531</v>
       </c>
     </row>
     <row r="884">
@@ -10722,7 +10719,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.30785942989023</v>
+        <v>-0.332846130020037</v>
       </c>
     </row>
     <row r="885">
@@ -10733,7 +10730,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.770692515656019</v>
+        <v>-0.437952602785062</v>
       </c>
     </row>
     <row r="886">
@@ -10744,7 +10741,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.205177396342139</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="887">
@@ -10755,7 +10752,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>0.050167951230504</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="888">
@@ -10766,7 +10763,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-1.7520731551459</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="889">
@@ -10777,7 +10774,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.118311044982285</v>
       </c>
     </row>
     <row r="890">
@@ -10788,7 +10785,7 @@
         <v>16</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.565099405519976</v>
+        <v>-0.830824678095617</v>
       </c>
     </row>
     <row r="891">
@@ -10799,7 +10796,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.159763313609467</v>
+        <v>-6.50482790567883</v>
       </c>
     </row>
     <row r="892">
@@ -10810,7 +10807,7 @@
         <v>16</v>
       </c>
       <c r="C892" t="n">
-        <v>-0.247717005914099</v>
+        <v>-0.351850772745273</v>
       </c>
     </row>
     <row r="893">
@@ -10821,7 +10818,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>0.0981236841224251</v>
+        <v>-0.18783902999694</v>
       </c>
     </row>
     <row r="894">
@@ -10832,7 +10829,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.46079022652522</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="895">
@@ -10843,7 +10840,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.363228765789661</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="896">
@@ -10854,7 +10851,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>-0.193876384410032</v>
+        <v>-0.192533080332128</v>
       </c>
     </row>
     <row r="897">
@@ -10865,7 +10862,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-1.29883165617858</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="898">
@@ -10876,7 +10873,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.0621173900235998</v>
+        <v>-0.963627656630563</v>
       </c>
     </row>
     <row r="899">
@@ -10887,7 +10884,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.96871024465042</v>
+        <v>-4.06331150848787</v>
       </c>
     </row>
     <row r="900">
@@ -10898,7 +10895,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.281470851925117</v>
+        <v>-0.270479748052596</v>
       </c>
     </row>
     <row r="901">
@@ -10909,7 +10906,7 @@
         <v>16</v>
       </c>
       <c r="C901" t="n">
-        <v>-0.752566228711823</v>
+        <v>-0.198269868808586</v>
       </c>
     </row>
     <row r="902">
@@ -10920,7 +10917,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>0.106454555524307</v>
+        <v>-1.14618786417739</v>
       </c>
     </row>
     <row r="903">
@@ -10931,7 +10928,7 @@
         <v>16</v>
       </c>
       <c r="C903" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.209692649523174</v>
       </c>
     </row>
     <row r="904">
@@ -10964,7 +10961,7 @@
         <v>16</v>
       </c>
       <c r="C906" t="n">
-        <v>-0.0195422299615298</v>
+        <v>-0.664501881284759</v>
       </c>
     </row>
     <row r="907">
@@ -10986,7 +10983,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.31475323413035</v>
+        <v>-0.613704976781143</v>
       </c>
     </row>
     <row r="909">
@@ -10997,7 +10994,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.803617829180213</v>
+        <v>-1.13080241733006</v>
       </c>
     </row>
     <row r="910">
@@ -11008,7 +11005,7 @@
         <v>16</v>
       </c>
       <c r="C910" t="n">
-        <v>-0.199080009666911</v>
+        <v>0.156649431736061</v>
       </c>
     </row>
     <row r="911">
@@ -11030,7 +11027,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>0.11041637231622</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="913">
@@ -11041,7 +11038,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>-0.360867839045011</v>
+        <v>-0.201838445758956</v>
       </c>
     </row>
     <row r="914">
@@ -11063,7 +11060,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>0.597029356332641</v>
+        <v>0.557214904806931</v>
       </c>
     </row>
     <row r="916">
@@ -11074,7 +11071,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-1.37553273593665</v>
+        <v>-0.594982303670018</v>
       </c>
     </row>
     <row r="917">
@@ -11085,7 +11082,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.268245109137446</v>
+        <v>-1.19949999779965</v>
       </c>
     </row>
     <row r="918">
@@ -11096,7 +11093,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.7835297475463</v>
+        <v>-0.616461399583784</v>
       </c>
     </row>
     <row r="919">
@@ -11118,7 +11115,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.269578019145935</v>
+        <v>-3.22673588815036</v>
       </c>
     </row>
     <row r="921">
@@ -11129,7 +11126,7 @@
         <v>16</v>
       </c>
       <c r="C921" t="n">
-        <v>-0.255348758390851</v>
+        <v>-0.183191610406549</v>
       </c>
     </row>
     <row r="922">
@@ -11140,7 +11137,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.868731542628123</v>
+        <v>-0.662596459766209</v>
       </c>
     </row>
     <row r="923">
@@ -11151,7 +11148,7 @@
         <v>16</v>
       </c>
       <c r="C923" t="n">
-        <v>-0.240347560718188</v>
+        <v>-0.186716100568598</v>
       </c>
     </row>
     <row r="924">
@@ -11162,7 +11159,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.112292604074672</v>
+        <v>-0.24075973693667</v>
       </c>
     </row>
     <row r="925">
@@ -11173,7 +11170,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.454279987657813</v>
+        <v>-1.1471275791148</v>
       </c>
     </row>
     <row r="926">
@@ -11195,7 +11192,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-1.23703964628507</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="928">
@@ -11206,7 +11203,7 @@
         <v>16</v>
       </c>
       <c r="C928" t="n">
-        <v>-0.530617854080956</v>
+        <v>0.0620788423996966</v>
       </c>
     </row>
     <row r="929">
@@ -11217,7 +11214,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.270262907897074</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="930">
@@ -11228,7 +11225,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.36332661799504</v>
       </c>
     </row>
     <row r="931">
@@ -11239,7 +11236,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.451948613202798</v>
+        <v>-0.286173768091744</v>
       </c>
     </row>
     <row r="932">
@@ -11250,7 +11247,7 @@
         <v>16</v>
       </c>
       <c r="C932" t="n">
-        <v>-0.502912369358202</v>
+        <v>-0.230431463099828</v>
       </c>
     </row>
     <row r="933">
@@ -11261,7 +11258,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>0.232231035609413</v>
+        <v>0.318602314385446</v>
       </c>
     </row>
     <row r="934">
@@ -11272,7 +11269,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>0.790290217980207</v>
+        <v>-0.498014902793342</v>
       </c>
     </row>
     <row r="935">
@@ -11294,7 +11291,7 @@
         <v>16</v>
       </c>
       <c r="C936" t="n">
-        <v>-0.448434632508015</v>
+        <v>-9.9237274280836</v>
       </c>
     </row>
     <row r="937">
@@ -11305,7 +11302,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.316634923363474</v>
+        <v>0.0812854590361722</v>
       </c>
     </row>
     <row r="938">
@@ -11316,7 +11313,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>0.68044260665654</v>
+        <v>0.64451399065496</v>
       </c>
     </row>
     <row r="939">
@@ -11327,7 +11324,7 @@
         <v>16</v>
       </c>
       <c r="C939" t="n">
-        <v>-2.72908217127543</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="940">
@@ -11338,7 +11335,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.467904182850798</v>
+        <v>0.0760507316638795</v>
       </c>
     </row>
     <row r="941">
@@ -11349,7 +11346,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.720167551173056</v>
+        <v>-0.483501183856998</v>
       </c>
     </row>
     <row r="942">
@@ -11360,7 +11357,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>-0.0534715974872049</v>
+        <v>-1.464061242098</v>
       </c>
     </row>
     <row r="943">
@@ -11371,7 +11368,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.929205228545611</v>
+        <v>-1.16332475725328</v>
       </c>
     </row>
     <row r="944">
@@ -11382,7 +11379,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.36200023361222</v>
       </c>
     </row>
     <row r="945">
@@ -11393,7 +11390,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-1.05168757730686</v>
+        <v>-1.0991111736353</v>
       </c>
     </row>
     <row r="946">
@@ -11415,7 +11412,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-1.61241658605262</v>
+        <v>-0.320863159874232</v>
       </c>
     </row>
     <row r="948">
@@ -11426,7 +11423,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-1.49511635080935</v>
+        <v>-0.717029676458822</v>
       </c>
     </row>
     <row r="949">
@@ -11437,7 +11434,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.235222359613396</v>
+        <v>-0.223170771498417</v>
       </c>
     </row>
     <row r="950">
@@ -11448,7 +11445,7 @@
         <v>16</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.713677459143938</v>
       </c>
     </row>
     <row r="951">
@@ -11470,7 +11467,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>-0.772476052861083</v>
+        <v>-1.05219451787429</v>
       </c>
     </row>
     <row r="953">
@@ -11481,7 +11478,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.470758910731006</v>
+        <v>-0.546786447940058</v>
       </c>
     </row>
     <row r="954">
@@ -11492,7 +11489,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.248011123507069</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="955">
@@ -11503,7 +11500,7 @@
         <v>16</v>
       </c>
       <c r="C955" t="n">
-        <v>-0.0936900887818897</v>
+        <v>-0.140901403255546</v>
       </c>
     </row>
     <row r="956">
@@ -11514,7 +11511,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.302623663289895</v>
+        <v>-1.94072478831255</v>
       </c>
     </row>
     <row r="957">
@@ -11525,7 +11522,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-1.01699788133691</v>
+        <v>-0.380275610881955</v>
       </c>
     </row>
     <row r="958">
@@ -11536,7 +11533,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.174049867229179</v>
+        <v>-0.538306693532954</v>
       </c>
     </row>
     <row r="959">
@@ -11547,7 +11544,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.193393499126398</v>
+        <v>-0.340337097185239</v>
       </c>
     </row>
     <row r="960">
@@ -11558,7 +11555,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.750516647963576</v>
+        <v>-0.690857189206348</v>
       </c>
     </row>
     <row r="961">
@@ -11569,7 +11566,7 @@
         <v>16</v>
       </c>
       <c r="C961" t="n">
-        <v>-0.134962223915896</v>
+        <v>-0.688409954338693</v>
       </c>
     </row>
     <row r="962">
@@ -11580,7 +11577,7 @@
         <v>16</v>
       </c>
       <c r="C962" t="n">
-        <v>-0.445041858680564</v>
+        <v>-6.96784223908752</v>
       </c>
     </row>
     <row r="963">
@@ -11591,7 +11588,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-0.893239511507598</v>
+        <v>-0.32560005298561</v>
       </c>
     </row>
     <row r="964">
@@ -11602,7 +11599,7 @@
         <v>16</v>
       </c>
       <c r="C964" t="n">
-        <v>-3.13148109103462</v>
+        <v>-0.286004169814798</v>
       </c>
     </row>
     <row r="965">
@@ -11613,7 +11610,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>-0.551477333554354</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="966">
@@ -11624,7 +11621,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.183496592493861</v>
+        <v>-0.342496786608794</v>
       </c>
     </row>
     <row r="967">
@@ -11635,7 +11632,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.557621727619914</v>
+        <v>-1.25441912769875</v>
       </c>
     </row>
     <row r="968">
@@ -11646,7 +11643,7 @@
         <v>16</v>
       </c>
       <c r="C968" t="n">
-        <v>-0.31328965360592</v>
+        <v>-0.200325132304217</v>
       </c>
     </row>
     <row r="969">
@@ -11657,7 +11654,7 @@
         <v>16</v>
       </c>
       <c r="C969" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.1677262776813</v>
       </c>
     </row>
     <row r="970">
@@ -11668,7 +11665,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.630862795565143</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="971">
@@ -11679,7 +11676,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.296601978344494</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="972">
@@ -11690,7 +11687,7 @@
         <v>16</v>
       </c>
       <c r="C972" t="n">
-        <v>-2.68033294332321</v>
+        <v>-0.579573309850982</v>
       </c>
     </row>
     <row r="973">
@@ -11701,7 +11698,7 @@
         <v>16</v>
       </c>
       <c r="C973" t="n">
-        <v>-0.271745658194188</v>
+        <v>-4.72462250993169</v>
       </c>
     </row>
     <row r="974">
@@ -11712,7 +11709,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.562765578847765</v>
       </c>
     </row>
     <row r="975">
@@ -11723,7 +11720,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.244060669683204</v>
+        <v>-0.327665983126164</v>
       </c>
     </row>
     <row r="976">
@@ -11734,7 +11731,7 @@
         <v>16</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.663136953170129</v>
       </c>
     </row>
     <row r="977">
@@ -11756,7 +11753,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>-0.977518660146836</v>
+        <v>-0.668389596484297</v>
       </c>
     </row>
     <row r="979">
@@ -11767,7 +11764,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>0.219316621255326</v>
+        <v>0.114562553812337</v>
       </c>
     </row>
     <row r="980">
@@ -11800,7 +11797,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.382068509426258</v>
+        <v>-0.177480470016254</v>
       </c>
     </row>
     <row r="983">
@@ -11811,7 +11808,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.132963919574765</v>
+        <v>-1.21527994471536</v>
       </c>
     </row>
     <row r="984">
@@ -11833,7 +11830,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-0.357703973628461</v>
+        <v>-0.384075181556478</v>
       </c>
     </row>
     <row r="986">
@@ -11844,7 +11841,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>0.166065751356711</v>
+        <v>-0.64803787823671</v>
       </c>
     </row>
     <row r="987">
@@ -11866,7 +11863,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.37175874569997</v>
+        <v>-0.723523929053402</v>
       </c>
     </row>
     <row r="989">
@@ -11877,7 +11874,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.159763313609468</v>
+        <v>-0.864699967334392</v>
       </c>
     </row>
     <row r="990">
@@ -11888,7 +11885,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.521296666997959</v>
+        <v>-1.08957855464058</v>
       </c>
     </row>
     <row r="991">
@@ -11899,7 +11896,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.02009506348903</v>
+        <v>-0.173585876342127</v>
       </c>
     </row>
     <row r="992">
@@ -11910,7 +11907,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-1.4188246106267</v>
+        <v>-1.03577286195149</v>
       </c>
     </row>
     <row r="993">
@@ -11932,7 +11929,7 @@
         <v>16</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.18977863099456</v>
       </c>
     </row>
     <row r="995">
@@ -11954,7 +11951,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.446977833130259</v>
+        <v>-0.0244081814375825</v>
       </c>
     </row>
     <row r="997">
@@ -11965,7 +11962,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.778531834515687</v>
+        <v>-0.393294018784712</v>
       </c>
     </row>
     <row r="998">
@@ -11976,7 +11973,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>0.163409995379336</v>
+        <v>-0.437066969383676</v>
       </c>
     </row>
     <row r="999">
@@ -11998,7 +11995,7 @@
         <v>16</v>
       </c>
       <c r="C1000" t="n">
-        <v>-0.299931550397882</v>
+        <v>-0.402997347893804</v>
       </c>
     </row>
     <row r="1001">
@@ -12009,7 +12006,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-0.209108381457065</v>
+        <v>-0.21066797396232</v>
       </c>
     </row>
     <row r="1002">
@@ -12020,7 +12017,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.549553017161507</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1003">
@@ -12031,7 +12028,7 @@
         <v>16</v>
       </c>
       <c r="C1003" t="n">
-        <v>-0.346205860518169</v>
+        <v>-0.247519879598553</v>
       </c>
     </row>
     <row r="1004">
@@ -12042,7 +12039,7 @@
         <v>16</v>
       </c>
       <c r="C1004" t="n">
-        <v>-0.301619523818377</v>
+        <v>-0.307904110070549</v>
       </c>
     </row>
     <row r="1005">
@@ -12053,7 +12050,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.288033116142643</v>
+        <v>-0.452190881721119</v>
       </c>
     </row>
     <row r="1006">
@@ -12064,7 +12061,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.963976366354318</v>
+        <v>-0.136238875980067</v>
       </c>
     </row>
     <row r="1007">
@@ -12075,7 +12072,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.51935892817447</v>
+        <v>-0.30445833707301</v>
       </c>
     </row>
     <row r="1008">
@@ -12086,7 +12083,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.423656360297102</v>
+        <v>-0.217170311680991</v>
       </c>
     </row>
     <row r="1009">
@@ -12097,7 +12094,7 @@
         <v>16</v>
       </c>
       <c r="C1009" t="n">
-        <v>-0.867913065762327</v>
+        <v>-0.539892925706533</v>
       </c>
     </row>
     <row r="1010">
@@ -12108,7 +12105,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-1.84946810985702</v>
+        <v>-1.32671741716812</v>
       </c>
     </row>
     <row r="1011">
@@ -12152,7 +12149,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.243592753586321</v>
+        <v>-0.397665821592998</v>
       </c>
     </row>
     <row r="1015">
@@ -12163,7 +12160,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.134138566567876</v>
+        <v>-0.938929340361179</v>
       </c>
     </row>
     <row r="1016">
@@ -12174,7 +12171,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.23852721460326</v>
       </c>
     </row>
     <row r="1017">
@@ -12185,7 +12182,7 @@
         <v>16</v>
       </c>
       <c r="C1017" t="n">
-        <v>-1.15233060661836</v>
+        <v>-1.13091154237818</v>
       </c>
     </row>
     <row r="1018">
@@ -12196,7 +12193,7 @@
         <v>16</v>
       </c>
       <c r="C1018" t="n">
-        <v>-0.249076890089004</v>
+        <v>-0.499163415428429</v>
       </c>
     </row>
     <row r="1019">
@@ -12207,7 +12204,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.552696291198227</v>
+        <v>-0.448716034699296</v>
       </c>
     </row>
     <row r="1020">
@@ -12229,7 +12226,7 @@
         <v>16</v>
       </c>
       <c r="C1021" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.345203599964134</v>
       </c>
     </row>
     <row r="1022">
@@ -12240,7 +12237,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.241156495036879</v>
+        <v>-0.379839641896709</v>
       </c>
     </row>
     <row r="1023">
@@ -12251,7 +12248,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.291262199772372</v>
+        <v>-0.0844275613607808</v>
       </c>
     </row>
     <row r="1024">
@@ -12262,7 +12259,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>-0.335782425842172</v>
+        <v>-0.604439036137031</v>
       </c>
     </row>
     <row r="1025">
@@ -12273,7 +12270,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.34588915833144</v>
       </c>
     </row>
     <row r="1026">
@@ -12295,7 +12292,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.760958147138852</v>
+        <v>-1.56729081191287</v>
       </c>
     </row>
     <row r="1028">
@@ -12306,7 +12303,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.53398811741307</v>
+        <v>-0.628672188728912</v>
       </c>
     </row>
     <row r="1029">
@@ -12317,7 +12314,7 @@
         <v>16</v>
       </c>
       <c r="C1029" t="n">
-        <v>-1.12904254064415</v>
+        <v>-0.198482115340026</v>
       </c>
     </row>
     <row r="1030">
@@ -12328,7 +12325,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.34972330325518</v>
       </c>
     </row>
     <row r="1031">
@@ -12339,7 +12336,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.186249180686152</v>
+        <v>-0.956067699196697</v>
       </c>
     </row>
     <row r="1032">
@@ -12350,7 +12347,7 @@
         <v>16</v>
       </c>
       <c r="C1032" t="n">
-        <v>-0.354984187929225</v>
+        <v>-0.847317699165877</v>
       </c>
     </row>
     <row r="1033">
@@ -12361,7 +12358,7 @@
         <v>16</v>
       </c>
       <c r="C1033" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.15137152129645</v>
       </c>
     </row>
     <row r="1034">
@@ -12372,7 +12369,7 @@
         <v>16</v>
       </c>
       <c r="C1034" t="n">
-        <v>-0.574379639455356</v>
+        <v>-0.857464225844608</v>
       </c>
     </row>
     <row r="1035">
@@ -12383,7 +12380,7 @@
         <v>16</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.293318821234672</v>
+        <v>-1.43037516731976</v>
       </c>
     </row>
     <row r="1036">
@@ -12394,7 +12391,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.783105481208202</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1037">
@@ -12405,7 +12402,7 @@
         <v>16</v>
       </c>
       <c r="C1037" t="n">
-        <v>-0.374852206343465</v>
+        <v>-1.3961513154914</v>
       </c>
     </row>
     <row r="1038">
@@ -12427,7 +12424,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.181762668904229</v>
+        <v>-0.298359858044643</v>
       </c>
     </row>
     <row r="1040">
@@ -12438,7 +12435,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.173611111111111</v>
+        <v>-3.26559903573116</v>
       </c>
     </row>
     <row r="1041">
@@ -12460,7 +12457,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.777198349779717</v>
+        <v>-0.343914745511103</v>
       </c>
     </row>
     <row r="1043">
@@ -12471,7 +12468,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-0.37185860005009</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1044">
@@ -12482,7 +12479,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.114198827144252</v>
+        <v>-0.321192057600672</v>
       </c>
     </row>
     <row r="1045">
@@ -12493,7 +12490,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.364968450086147</v>
       </c>
     </row>
     <row r="1046">
@@ -12504,7 +12501,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.19568363865326</v>
       </c>
     </row>
     <row r="1047">
@@ -12515,7 +12512,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.424215560990194</v>
+        <v>-0.485053579966328</v>
       </c>
     </row>
     <row r="1048">
@@ -12526,7 +12523,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.180728894558793</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1049">
@@ -12537,7 +12534,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.318492677660844</v>
+        <v>-0.462979399720655</v>
       </c>
     </row>
     <row r="1050">
@@ -12548,7 +12545,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.556135014824869</v>
       </c>
     </row>
     <row r="1051">
@@ -12570,7 +12567,7 @@
         <v>16</v>
       </c>
       <c r="C1052" t="n">
-        <v>-0.214093300664027</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1053">
@@ -12581,7 +12578,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.2546489360403</v>
+        <v>-0.639452076589647</v>
       </c>
     </row>
     <row r="1054">
@@ -12592,7 +12589,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.0754729885811434</v>
       </c>
     </row>
     <row r="1055">
@@ -12603,7 +12600,7 @@
         <v>16</v>
       </c>
       <c r="C1055" t="n">
-        <v>-0.0795878245551658</v>
+        <v>-0.578264095381747</v>
       </c>
     </row>
     <row r="1056">
@@ -12614,7 +12611,7 @@
         <v>16</v>
       </c>
       <c r="C1056" t="n">
-        <v>-0.173611111111111</v>
+        <v>0.158026868365752</v>
       </c>
     </row>
     <row r="1057">
@@ -12625,7 +12622,7 @@
         <v>16</v>
       </c>
       <c r="C1057" t="n">
-        <v>-0.244948568857141</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1058">
@@ -12658,7 +12655,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.202297161331868</v>
+        <v>-0.189339841060875</v>
       </c>
     </row>
     <row r="1061">
@@ -12669,7 +12666,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.540053003453153</v>
+        <v>-1.04457345901037</v>
       </c>
     </row>
     <row r="1062">
@@ -12680,7 +12677,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.934849583396527</v>
+        <v>-1.85820663867551</v>
       </c>
     </row>
     <row r="1063">
@@ -12691,7 +12688,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.959707741839376</v>
+        <v>-0.0666629984051885</v>
       </c>
     </row>
     <row r="1064">
@@ -12702,7 +12699,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.0426297150205452</v>
       </c>
     </row>
     <row r="1065">
@@ -12713,7 +12710,7 @@
         <v>16</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.253769673829934</v>
+        <v>-0.463095749210106</v>
       </c>
     </row>
     <row r="1066">
@@ -12724,7 +12721,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-1.12538912984013</v>
+        <v>-1.09423571495523</v>
       </c>
     </row>
     <row r="1067">
@@ -12735,7 +12732,7 @@
         <v>16</v>
       </c>
       <c r="C1067" t="n">
-        <v>-0.37640887125465</v>
+        <v>-0.221014716147145</v>
       </c>
     </row>
     <row r="1068">
@@ -12746,7 +12743,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.58632571808431</v>
+        <v>-0.343636054321831</v>
       </c>
     </row>
     <row r="1069">
@@ -12768,7 +12765,7 @@
         <v>16</v>
       </c>
       <c r="C1070" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.0371528742934479</v>
       </c>
     </row>
     <row r="1071">
@@ -12779,7 +12776,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.39203505410218</v>
       </c>
     </row>
     <row r="1072">
@@ -12790,7 +12787,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.254118633057484</v>
+        <v>0.0173513716661891</v>
       </c>
     </row>
     <row r="1073">
@@ -12801,7 +12798,7 @@
         <v>16</v>
       </c>
       <c r="C1073" t="n">
-        <v>-0.597410775071195</v>
+        <v>-0.366912009155958</v>
       </c>
     </row>
     <row r="1074">
@@ -12812,7 +12809,7 @@
         <v>16</v>
       </c>
       <c r="C1074" t="n">
-        <v>-0.239232587992527</v>
+        <v>-0.775774773206024</v>
       </c>
     </row>
     <row r="1075">
@@ -12823,7 +12820,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-1.81838714675943</v>
+        <v>-0.946398297398723</v>
       </c>
     </row>
     <row r="1076">
@@ -12834,7 +12831,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.377805049201909</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1077">
@@ -12845,7 +12842,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.515610871447556</v>
+        <v>-0.135023240646866</v>
       </c>
     </row>
     <row r="1078">
@@ -12856,7 +12853,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.35968948207668</v>
+        <v>0.189326148577436</v>
       </c>
     </row>
     <row r="1079">
@@ -12867,7 +12864,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.527462410923402</v>
+        <v>-0.0877225814508005</v>
       </c>
     </row>
     <row r="1080">
@@ -12878,7 +12875,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.306085245492197</v>
+        <v>-0.349122123640957</v>
       </c>
     </row>
     <row r="1081">
@@ -12889,7 +12886,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.918824568986408</v>
       </c>
     </row>
     <row r="1082">
@@ -12900,7 +12897,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.391547200412909</v>
+        <v>-0.292878480648298</v>
       </c>
     </row>
     <row r="1083">
@@ -12911,7 +12908,7 @@
         <v>16</v>
       </c>
       <c r="C1083" t="n">
-        <v>-0.302202207186532</v>
+        <v>-0.272165100840256</v>
       </c>
     </row>
     <row r="1084">
@@ -12922,7 +12919,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.720895797945923</v>
+        <v>-0.582698663783291</v>
       </c>
     </row>
     <row r="1085">
@@ -12933,7 +12930,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>-0.333495695740432</v>
+        <v>-0.58631932820798</v>
       </c>
     </row>
     <row r="1086">
@@ -12944,7 +12941,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.462335655672792</v>
       </c>
     </row>
     <row r="1087">
@@ -12955,7 +12952,7 @@
         <v>16</v>
       </c>
       <c r="C1087" t="n">
-        <v>-0.291247153105979</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1088">
@@ -12966,7 +12963,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.396026703629252</v>
+        <v>-0.122546379360092</v>
       </c>
     </row>
     <row r="1089">
@@ -12977,7 +12974,7 @@
         <v>16</v>
       </c>
       <c r="C1089" t="n">
-        <v>-0.442519162391114</v>
+        <v>-8.64740891216553</v>
       </c>
     </row>
     <row r="1090">
@@ -12988,7 +12985,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.428583486121491</v>
+        <v>-0.324024295031827</v>
       </c>
     </row>
     <row r="1091">
@@ -12999,7 +12996,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.276001727257005</v>
+        <v>0.841217796794996</v>
       </c>
     </row>
     <row r="1092">
@@ -13010,7 +13007,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.206745752698319</v>
+        <v>-1.17630043960944</v>
       </c>
     </row>
     <row r="1093">
@@ -13021,7 +13018,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.192533833713041</v>
+        <v>-0.186425091823808</v>
       </c>
     </row>
     <row r="1094">
@@ -13032,7 +13029,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-0.791229111935255</v>
+        <v>-0.57748846451877</v>
       </c>
     </row>
     <row r="1095">
@@ -13043,7 +13040,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.218386916054595</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1096">
@@ -13054,7 +13051,7 @@
         <v>16</v>
       </c>
       <c r="C1096" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.23283508421436</v>
       </c>
     </row>
     <row r="1097">
@@ -13065,7 +13062,7 @@
         <v>16</v>
       </c>
       <c r="C1097" t="n">
-        <v>-0.0709872130945677</v>
+        <v>-0.459074723813509</v>
       </c>
     </row>
     <row r="1098">
@@ -13076,7 +13073,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.30160381418183</v>
       </c>
     </row>
     <row r="1099">
@@ -13098,7 +13095,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>-0.401171455344834</v>
+        <v>-0.175006184713512</v>
       </c>
     </row>
     <row r="1101">
@@ -13109,7 +13106,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.293894412983599</v>
+        <v>0.305196376339884</v>
       </c>
     </row>
     <row r="1102">
@@ -13120,7 +13117,7 @@
         <v>16</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.973734499851967</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1103">
@@ -13142,7 +13139,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.924654973628794</v>
+        <v>-0.902293411571324</v>
       </c>
     </row>
     <row r="1105">
@@ -13153,7 +13150,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.667868522575631</v>
+        <v>-1.09986079327263</v>
       </c>
     </row>
     <row r="1106">
@@ -13164,7 +13161,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.666312859708392</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1107">
@@ -13175,7 +13172,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.294734265724081</v>
+        <v>-0.359596328255647</v>
       </c>
     </row>
     <row r="1108">
@@ -13208,7 +13205,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.245527703312104</v>
+        <v>-0.235508334204825</v>
       </c>
     </row>
     <row r="1111">
@@ -13219,7 +13216,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-1.52591672968036</v>
+        <v>-0.151130263907427</v>
       </c>
     </row>
     <row r="1112">
@@ -13230,7 +13227,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.0917948814130649</v>
       </c>
     </row>
     <row r="1113">
@@ -13252,7 +13249,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>0.500463599449835</v>
+        <v>0.162872129456672</v>
       </c>
     </row>
     <row r="1115">
@@ -13274,7 +13271,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.493355789118216</v>
+        <v>-0.496025576245001</v>
       </c>
     </row>
     <row r="1117">
@@ -13285,7 +13282,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.245386962028177</v>
+        <v>-0.245716757707513</v>
       </c>
     </row>
     <row r="1118">
@@ -13296,7 +13293,7 @@
         <v>16</v>
       </c>
       <c r="C1118" t="n">
-        <v>-1.07474737438366</v>
+        <v>-0.311942179154349</v>
       </c>
     </row>
     <row r="1119">
@@ -13307,7 +13304,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.387292226698327</v>
+        <v>-0.283135530931743</v>
       </c>
     </row>
     <row r="1120">
@@ -13318,7 +13315,7 @@
         <v>16</v>
       </c>
       <c r="C1120" t="n">
-        <v>-0.51956700440714</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1121">
@@ -13329,7 +13326,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.57164938215319</v>
+        <v>-1.73629715191915</v>
       </c>
     </row>
     <row r="1122">
@@ -13340,7 +13337,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>0.0960994801382203</v>
+        <v>0.291993856873783</v>
       </c>
     </row>
     <row r="1123">
@@ -13351,7 +13348,7 @@
         <v>16</v>
       </c>
       <c r="C1123" t="n">
-        <v>-1.46286490074848</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1124">
@@ -13362,7 +13359,7 @@
         <v>16</v>
       </c>
       <c r="C1124" t="n">
-        <v>-0.207091094275596</v>
+        <v>-0.29037751102768</v>
       </c>
     </row>
     <row r="1125">
@@ -13373,7 +13370,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-0.32772080479205</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1126">
@@ -13384,7 +13381,7 @@
         <v>16</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.173611111111111</v>
+        <v>-2.00376758596604</v>
       </c>
     </row>
     <row r="1127">
@@ -13395,7 +13392,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.462208285920516</v>
+        <v>-0.238005850621798</v>
       </c>
     </row>
     <row r="1128">
@@ -13406,7 +13403,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.145987775124928</v>
+        <v>-0.045568410581877</v>
       </c>
     </row>
     <row r="1129">
@@ -13417,7 +13414,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.24089403755797</v>
       </c>
     </row>
     <row r="1130">
@@ -13428,7 +13425,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.208713200088111</v>
+        <v>-0.168852080892405</v>
       </c>
     </row>
     <row r="1131">
@@ -13439,7 +13436,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.294472797038231</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1132">
@@ -13461,7 +13458,7 @@
         <v>16</v>
       </c>
       <c r="C1133" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.297955062535628</v>
       </c>
     </row>
     <row r="1134">
@@ -13472,7 +13469,7 @@
         <v>16</v>
       </c>
       <c r="C1134" t="n">
-        <v>-0.217874451426749</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1135">
@@ -13483,7 +13480,7 @@
         <v>16</v>
       </c>
       <c r="C1135" t="n">
-        <v>-0.792652084065411</v>
+        <v>-0.224611366276629</v>
       </c>
     </row>
     <row r="1136">
@@ -13494,7 +13491,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.34154473989171</v>
+        <v>-0.539646374006845</v>
       </c>
     </row>
     <row r="1137">
@@ -13505,7 +13502,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.12937974886362</v>
       </c>
     </row>
     <row r="1138">
@@ -13516,7 +13513,7 @@
         <v>16</v>
       </c>
       <c r="C1138" t="n">
-        <v>-0.226059794842687</v>
+        <v>-0.442984249007773</v>
       </c>
     </row>
     <row r="1139">
@@ -13527,7 +13524,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.182164813056211</v>
+        <v>-0.158723067692552</v>
       </c>
     </row>
     <row r="1140">
@@ -13538,7 +13535,7 @@
         <v>16</v>
       </c>
       <c r="C1140" t="n">
-        <v>-0.329899600581766</v>
+        <v>-0.820703053640712</v>
       </c>
     </row>
     <row r="1141">
@@ -13549,7 +13546,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.434709545579847</v>
+        <v>-0.196124134203649</v>
       </c>
     </row>
     <row r="1142">
@@ -13560,7 +13557,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.224509466067572</v>
+        <v>0.392691345377833</v>
       </c>
     </row>
     <row r="1143">
@@ -13571,7 +13568,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.162253665376636</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1144">
@@ -13582,7 +13579,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.318157811551909</v>
+        <v>-0.574475068817403</v>
       </c>
     </row>
     <row r="1145">
@@ -13593,7 +13590,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.0999550784325351</v>
       </c>
     </row>
     <row r="1146">
@@ -13604,7 +13601,7 @@
         <v>16</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.158540213927637</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1147">
@@ -13615,7 +13612,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.119190681344333</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1148">
@@ -13626,7 +13623,7 @@
         <v>16</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.353997184994757</v>
+        <v>-0.242788127308044</v>
       </c>
     </row>
     <row r="1149">
@@ -13637,7 +13634,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.242540161415529</v>
       </c>
     </row>
     <row r="1150">
@@ -13659,7 +13656,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.246296158903736</v>
+        <v>0.483831329724288</v>
       </c>
     </row>
     <row r="1152">
@@ -13681,7 +13678,7 @@
         <v>16</v>
       </c>
       <c r="C1153" t="n">
-        <v>0.29012185448404</v>
+        <v>0.133058544483298</v>
       </c>
     </row>
     <row r="1154">
@@ -13692,7 +13689,7 @@
         <v>16</v>
       </c>
       <c r="C1154" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.183951006117216</v>
       </c>
     </row>
     <row r="1155">
@@ -13714,7 +13711,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.212001323979873</v>
       </c>
     </row>
     <row r="1157">
@@ -13725,7 +13722,7 @@
         <v>16</v>
       </c>
       <c r="C1157" t="n">
-        <v>-1.96991499955425</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1158">
@@ -13736,7 +13733,7 @@
         <v>16</v>
       </c>
       <c r="C1158" t="n">
-        <v>-0.267637501137523</v>
+        <v>-0.451630343993635</v>
       </c>
     </row>
     <row r="1159">
@@ -13747,7 +13744,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-0.599070274405712</v>
+        <v>-0.618067925679131</v>
       </c>
     </row>
     <row r="1160">
@@ -13758,7 +13755,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.713467537362142</v>
+        <v>-0.832056209585314</v>
       </c>
     </row>
     <row r="1161">
@@ -13769,7 +13766,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>0.198722587131693</v>
+        <v>0.148312921422925</v>
       </c>
     </row>
     <row r="1162">
@@ -13791,7 +13788,7 @@
         <v>16</v>
       </c>
       <c r="C1163" t="n">
-        <v>-0.226162187643797</v>
+        <v>-1.97385373859596</v>
       </c>
     </row>
     <row r="1164">
@@ -13802,7 +13799,7 @@
         <v>16</v>
       </c>
       <c r="C1164" t="n">
-        <v>-0.254011808900376</v>
+        <v>-0.8403486946341</v>
       </c>
     </row>
     <row r="1165">
@@ -13813,7 +13810,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.411912668549834</v>
       </c>
     </row>
     <row r="1166">
@@ -13824,7 +13821,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.173611111111111</v>
+        <v>-1.47227322058875</v>
       </c>
     </row>
     <row r="1167">
@@ -13835,7 +13832,7 @@
         <v>16</v>
       </c>
       <c r="C1167" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.475996736291973</v>
       </c>
     </row>
     <row r="1168">
@@ -13846,7 +13843,7 @@
         <v>16</v>
       </c>
       <c r="C1168" t="n">
-        <v>-0.183554687884797</v>
+        <v>-0.196068515388017</v>
       </c>
     </row>
     <row r="1169">
@@ -13857,7 +13854,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.306880521402545</v>
+        <v>-4.84471733207733</v>
       </c>
     </row>
     <row r="1170">
@@ -13868,7 +13865,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.0114775861785419</v>
+        <v>-0.235956236843702</v>
       </c>
     </row>
     <row r="1171">
@@ -13879,7 +13876,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>-0.126867648939083</v>
+        <v>-0.214173641990919</v>
       </c>
     </row>
     <row r="1172">
@@ -13890,7 +13887,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.901192702126161</v>
       </c>
     </row>
     <row r="1173">
@@ -13901,7 +13898,7 @@
         <v>16</v>
       </c>
       <c r="C1173" t="n">
-        <v>-0.20462389395664</v>
+        <v>-0.634251355033642</v>
       </c>
     </row>
     <row r="1174">
@@ -13912,7 +13909,7 @@
         <v>16</v>
       </c>
       <c r="C1174" t="n">
-        <v>0.245865712435281</v>
+        <v>-0.063194289372378</v>
       </c>
     </row>
     <row r="1175">
@@ -13923,7 +13920,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.556361346251796</v>
+        <v>-3.20884267147526</v>
       </c>
     </row>
     <row r="1176">
@@ -13934,7 +13931,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.663982716236682</v>
       </c>
     </row>
     <row r="1177">
@@ -13945,7 +13942,7 @@
         <v>16</v>
       </c>
       <c r="C1177" t="n">
-        <v>-0.504184831273175</v>
+        <v>-0.607380288976109</v>
       </c>
     </row>
     <row r="1178">
@@ -13967,7 +13964,7 @@
         <v>16</v>
       </c>
       <c r="C1179" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.220518360433007</v>
       </c>
     </row>
     <row r="1180">
@@ -13978,7 +13975,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-1.03444048266112</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1181">
@@ -13989,7 +13986,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.600482440798956</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
     <row r="1182">
@@ -14000,7 +13997,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.75428123097746</v>
       </c>
     </row>
     <row r="1183">
@@ -14011,7 +14008,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.185817732951543</v>
+        <v>-0.152639469189351</v>
       </c>
     </row>
     <row r="1184">
@@ -14033,7 +14030,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.859198084086246</v>
       </c>
     </row>
     <row r="1186">
@@ -14044,7 +14041,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.331286031510456</v>
+        <v>-0.853486818059542</v>
       </c>
     </row>
     <row r="1187">
@@ -14066,7 +14063,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.315003909026913</v>
+        <v>-0.804319917726538</v>
       </c>
     </row>
     <row r="1189">
@@ -14077,7 +14074,7 @@
         <v>16</v>
       </c>
       <c r="C1189" t="n">
-        <v>-0.173611111111111</v>
+        <v>-0.482558790373664</v>
       </c>
     </row>
     <row r="1190">
@@ -14088,7 +14085,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.203666681012618</v>
+        <v>-0.222156181098863</v>
       </c>
     </row>
     <row r="1191">
@@ -14099,7 +14096,7 @@
         <v>16</v>
       </c>
       <c r="C1191" t="n">
-        <v>-0.259969785001229</v>
+        <v>-0.925168902548902</v>
       </c>
     </row>
     <row r="1192">
@@ -14110,7 +14107,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-1.22286016325342</v>
+        <v>-0.526912190217531</v>
       </c>
     </row>
     <row r="1193">
@@ -14121,7 +14118,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.23431688696736</v>
+        <v>-0.900131238714398</v>
       </c>
     </row>
     <row r="1194">
@@ -14143,7 +14140,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.375965377019392</v>
+        <v>-0.850172464835007</v>
       </c>
     </row>
     <row r="1196">
@@ -14154,7 +14151,7 @@
         <v>16</v>
       </c>
       <c r="C1196" t="n">
-        <v>-0.582702900097896</v>
+        <v>-0.583199197876874</v>
       </c>
     </row>
     <row r="1197">
@@ -14165,7 +14162,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.471198139711428</v>
+        <v>-0.535403528155027</v>
       </c>
     </row>
     <row r="1198">
@@ -14176,7 +14173,7 @@
         <v>16</v>
       </c>
       <c r="C1198" t="n">
-        <v>-0.800173959595069</v>
+        <v>-0.970272719867487</v>
       </c>
     </row>
     <row r="1199">
@@ -14187,7 +14184,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.457234687412434</v>
+        <v>-0.480665990511338</v>
       </c>
     </row>
     <row r="1200">
@@ -14198,7 +14195,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-0.771292398003421</v>
+        <v>-0.927029417190047</v>
       </c>
     </row>
     <row r="1201">
@@ -14209,7 +14206,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-1.10324792014178</v>
+        <v>-0.173611111111111</v>
       </c>
     </row>
   </sheetData>
@@ -14764,7 +14761,7 @@
         <v>2790.83</v>
       </c>
       <c r="E32" t="n">
-        <v>-448.374694161591</v>
+        <v>-179.339230769231</v>
       </c>
     </row>
     <row r="33">
@@ -14934,7 +14931,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E42" t="n">
-        <v>2920.83637806431</v>
+        <v>1419.3243623118</v>
       </c>
     </row>
     <row r="43">
@@ -15087,7 +15084,7 @@
         <v>-1.918</v>
       </c>
       <c r="E51" t="n">
-        <v>2.50232707956311</v>
+        <v>2.12738461538462</v>
       </c>
     </row>
     <row r="52">
@@ -15223,7 +15220,7 @@
         <v>83</v>
       </c>
       <c r="E59" t="n">
-        <v>39.3846153846154</v>
+        <v>15.6065463465495</v>
       </c>
     </row>
     <row r="60">
@@ -15342,7 +15339,7 @@
         <v>5</v>
       </c>
       <c r="E66" t="n">
-        <v>49.0635893912072</v>
+        <v>45.3846153846154</v>
       </c>
     </row>
     <row r="67">
@@ -15410,7 +15407,7 @@
         <v>5</v>
       </c>
       <c r="E70" t="n">
-        <v>122.121247642536</v>
+        <v>118.18530753624</v>
       </c>
     </row>
     <row r="71">
@@ -15444,7 +15441,7 @@
         <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>9.25</v>
+        <v>-2.83694741146374</v>
       </c>
     </row>
     <row r="73">
@@ -15631,7 +15628,7 @@
         <v>15</v>
       </c>
       <c r="E83" t="n">
-        <v>5.435514091232</v>
+        <v>8.41666666666667</v>
       </c>
     </row>
     <row r="84">
@@ -15769,16 +15766,16 @@
         <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
@@ -15786,16 +15783,16 @@
         <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E8" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
@@ -15803,16 +15800,16 @@
         <v>16</v>
       </c>
       <c r="B9" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -15820,16 +15817,16 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -15837,16 +15834,16 @@
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.142857142857143</v>
       </c>
       <c r="E11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12">
@@ -15854,7 +15851,7 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="C12" t="n">
         <v>1</v>
@@ -15863,7 +15860,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13">
@@ -15871,7 +15868,7 @@
         <v>16</v>
       </c>
       <c r="B13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C13" t="n">
         <v>1</v>
@@ -15880,7 +15877,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14">
@@ -15888,7 +15885,7 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -15897,7 +15894,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15">
@@ -15905,7 +15902,7 @@
         <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -15914,7 +15911,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -15931,7 +15928,7 @@
         <v>0.0714285714285714</v>
       </c>
       <c r="E16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -15942,10 +15939,10 @@
         <v>52</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="E17" t="s">
         <v>20</v>
@@ -15962,10 +15959,10 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -15973,16 +15970,16 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C19" t="n">
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E19" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
@@ -15990,117 +15987,15 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="C20" t="n">
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0714285714285714</v>
+        <v>0.0769230769230769</v>
       </c>
       <c r="E20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" t="s">
-        <v>49</v>
-      </c>
-      <c r="C21" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E21" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E22" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" t="s">
-        <v>51</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E23" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E24" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C25" t="n">
-        <v>1</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="E25" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" t="s">
-        <v>47</v>
-      </c>
-      <c r="C26" t="n">
-        <v>1</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0769230769230769</v>
-      </c>
-      <c r="E26" t="s">
         <v>21</v>
       </c>
     </row>
